--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -410,18 +410,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -746,7 +740,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -770,16 +764,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -788,125 +782,129 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1229,290 +1227,290 @@
   <dimension ref="A1:V30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="3" customWidth="1"/>
+    <col min="1" max="1" width="2.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="4" customWidth="1"/>
     <col min="3" max="3" width="3.125" style="1" customWidth="1"/>
     <col min="4" max="5" width="9.875" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="24.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="23.375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="23.625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="30" style="4" customWidth="1"/>
-    <col min="13" max="13" width="26.875" style="4" customWidth="1"/>
-    <col min="14" max="14" width="8.375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="8.875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="6.375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="8" style="3" customWidth="1"/>
-    <col min="18" max="19" width="7.25" style="3" customWidth="1"/>
-    <col min="20" max="20" width="9.75" style="3" customWidth="1"/>
-    <col min="21" max="21" width="12.875" style="3" customWidth="1"/>
-    <col min="22" max="22" width="13.375" style="3" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="3"/>
+    <col min="8" max="8" width="22.875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="24.125" style="5" customWidth="1"/>
+    <col min="10" max="10" width="23.375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="23.625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="30" style="5" customWidth="1"/>
+    <col min="13" max="13" width="26.875" style="5" customWidth="1"/>
+    <col min="14" max="14" width="8.375" style="4" customWidth="1"/>
+    <col min="15" max="15" width="8.875" style="4" customWidth="1"/>
+    <col min="16" max="16" width="6.375" style="4" customWidth="1"/>
+    <col min="17" max="17" width="8" style="4" customWidth="1"/>
+    <col min="18" max="19" width="7.25" style="4" customWidth="1"/>
+    <col min="20" max="20" width="9.75" style="4" customWidth="1"/>
+    <col min="21" max="21" width="12.875" style="4" customWidth="1"/>
+    <col min="22" max="22" width="13.375" style="4" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="13" t="s">
+      <c r="U3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="V3" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="6" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="V5" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>25</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>165000</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <v>30000</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="10">
         <v>33000</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="10">
         <v>6000</v>
       </c>
-      <c r="L6" s="9">
+      <c r="L6" s="10">
         <v>16500000</v>
       </c>
-      <c r="M6" s="9">
+      <c r="M6" s="10">
         <v>3000000</v>
       </c>
       <c r="N6" s="2">
@@ -1536,45 +1534,45 @@
       <c r="T6" s="2">
         <v>0</v>
       </c>
-      <c r="U6" s="15" t="s">
+      <c r="U6" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="V6" s="15" t="s">
+      <c r="V6" s="17" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <v>2</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <v>26</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="9">
         <v>50</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <v>11600000</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="10">
         <v>2320000</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="L7" s="9">
+      <c r="L7" s="10">
         <v>1160000000</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="18" t="s">
         <v>28</v>
       </c>
       <c r="N7" s="2">
@@ -1598,45 +1596,45 @@
       <c r="T7" s="2">
         <v>0</v>
       </c>
-      <c r="U7" s="15" t="s">
+      <c r="U7" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="V7" s="15" t="s">
+      <c r="V7" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C8" s="8">
+      <c r="C8" s="9">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>1</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>51</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <v>75</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <v>837025000</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="I8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="10">
         <v>167405000</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="10">
         <v>83702500000</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="18" t="s">
         <v>32</v>
       </c>
       <c r="N8" s="2">
@@ -1660,57 +1658,57 @@
       <c r="T8" s="2">
         <v>0</v>
       </c>
-      <c r="U8" s="15" t="s">
+      <c r="U8" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="V8" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <v>4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>76</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <v>100</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <v>58655700000</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="10">
         <v>11731140000</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="9">
+      <c r="L9" s="10">
         <v>16863800000000</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="18" t="s">
         <v>36</v>
       </c>
       <c r="N9" s="2">
         <v>75</v>
       </c>
-      <c r="O9" s="1">
+      <c r="O9" s="12">
         <v>10</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="12">
         <v>15</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="12">
         <v>15</v>
       </c>
       <c r="R9" s="2">
@@ -1722,71 +1720,71 @@
       <c r="T9" s="2">
         <v>0</v>
       </c>
-      <c r="U9" s="15" t="s">
+      <c r="U9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="V9" s="15" t="s">
+      <c r="V9" s="17" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:21">
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="U10" s="14"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="U10" s="16"/>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <v>11</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="9">
         <v>2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>1</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="9">
         <v>25</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="10">
         <v>70000000000</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="11">
         <v>35000000000</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="10">
         <v>1000000000</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="11">
         <v>1400000000000000</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="11">
+      <c r="N11" s="3">
         <v>135</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="3">
         <v>65</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="3">
         <v>100</v>
       </c>
-      <c r="Q11" s="11">
+      <c r="Q11" s="3">
         <v>100</v>
       </c>
       <c r="R11" s="2">
@@ -1798,57 +1796,57 @@
       <c r="T11" s="2">
         <v>0</v>
       </c>
-      <c r="U11" s="15" t="s">
+      <c r="U11" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="V11" s="15" t="s">
+      <c r="V11" s="17" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C12" s="8">
+      <c r="C12" s="9">
         <v>12</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="9">
         <v>2</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="9">
         <v>26</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="9">
         <v>50</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="11">
         <v>400000000000</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="10">
         <v>30000000000</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="11">
         <v>80000000000</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="10">
         <v>6000000000</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="11">
         <v>8000000000000000</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="10">
         <v>600000000000000</v>
       </c>
-      <c r="N12" s="11">
+      <c r="N12" s="3">
         <v>160</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="3">
         <v>90</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="11">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
       <c r="R12" s="2">
@@ -1860,57 +1858,57 @@
       <c r="T12" s="2">
         <v>0</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="U12" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="V12" s="15" t="s">
+      <c r="V12" s="17" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <v>13</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9">
         <v>2</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="9">
         <v>51</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="9">
         <v>75</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="11">
         <v>2200000000000</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="10">
         <v>100000000000</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="10">
         <v>440000000000</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="10">
         <v>20000000000</v>
       </c>
-      <c r="L13" s="9">
+      <c r="L13" s="10">
         <v>4.4e+16</v>
       </c>
-      <c r="M13" s="9">
+      <c r="M13" s="10">
         <v>2000000000000000</v>
       </c>
-      <c r="N13" s="11">
+      <c r="N13" s="3">
         <v>185</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="3">
         <v>115</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="3">
         <v>100</v>
       </c>
-      <c r="Q13" s="11">
+      <c r="Q13" s="3">
         <v>100</v>
       </c>
       <c r="R13" s="2">
@@ -1922,57 +1920,57 @@
       <c r="T13" s="2">
         <v>0</v>
       </c>
-      <c r="U13" s="15" t="s">
+      <c r="U13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="V13" s="15" t="s">
+      <c r="V13" s="17" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <v>14</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <v>2</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <v>76</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <v>100</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="11">
         <v>12000000000000</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <v>1000000000000</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="10">
         <v>2400000000000</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="10">
         <v>200000000000</v>
       </c>
-      <c r="L14" s="9">
+      <c r="L14" s="10">
         <v>2.4e+17</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M14" s="10">
         <v>2e+16</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="3">
         <v>209</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="3">
         <v>139</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="11">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
       <c r="R14" s="2">
@@ -1984,58 +1982,58 @@
       <c r="T14" s="2">
         <v>0</v>
       </c>
-      <c r="U14" s="15" t="s">
+      <c r="U14" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="V14" s="15" t="s">
+      <c r="V14" s="17" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C16" s="8">
+      <c r="C16" s="9">
         <v>21</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9">
         <v>3</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="9">
         <v>1</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="9">
         <v>25</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="10">
         <v>70000000000000</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="10">
         <v>280000000000000</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="10">
         <v>350000000000000</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="10">
         <v>1400000000000000</v>
       </c>
-      <c r="L16" s="9">
+      <c r="L16" s="10">
         <v>1.4e+19</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M16" s="10">
         <v>5.6e+19</v>
       </c>
       <c r="N16" s="2">
@@ -2059,45 +2057,45 @@
       <c r="T16" s="2">
         <v>80</v>
       </c>
-      <c r="U16" s="15" t="s">
+      <c r="U16" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="V16" s="15" t="s">
+      <c r="V16" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C17" s="8">
+      <c r="C17" s="9">
         <v>22</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="9">
         <v>3</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="9">
         <v>26</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="9">
         <v>50</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="10">
         <v>700000000000000</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="10">
         <v>2800000000000000</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="10">
         <v>3500000000000000</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="10">
         <v>1.4e+16</v>
       </c>
-      <c r="L17" s="9">
+      <c r="L17" s="10">
         <v>1.4e+20</v>
       </c>
-      <c r="M17" s="9">
+      <c r="M17" s="10">
         <v>5.6e+20</v>
       </c>
       <c r="N17" s="2">
@@ -2121,45 +2119,45 @@
       <c r="T17" s="2">
         <v>80</v>
       </c>
-      <c r="U17" s="15" t="s">
+      <c r="U17" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="V17" s="15" t="s">
+      <c r="V17" s="17" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <v>23</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <v>3</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>51</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <v>75</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <v>7000000000000000</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="10">
         <v>2.8e+16</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="10">
         <v>3.5e+16</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="10">
         <v>1.4e+17</v>
       </c>
-      <c r="L18" s="9">
+      <c r="L18" s="10">
         <v>1.4e+21</v>
       </c>
-      <c r="M18" s="9">
+      <c r="M18" s="10">
         <v>5.6e+21</v>
       </c>
       <c r="N18" s="2">
@@ -2183,45 +2181,45 @@
       <c r="T18" s="2">
         <v>80</v>
       </c>
-      <c r="U18" s="15" t="s">
+      <c r="U18" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="V18" s="15" t="s">
+      <c r="V18" s="17" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <v>24</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <v>3</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <v>76</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <v>100</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="10">
         <v>7e+16</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="10">
         <v>2.8e+17</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="10">
         <v>3.5e+17</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="10">
         <v>1.4e+18</v>
       </c>
-      <c r="L19" s="9">
+      <c r="L19" s="10">
         <v>1.4e+22</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M19" s="10">
         <v>5.6e+22</v>
       </c>
       <c r="N19" s="2">
@@ -2245,54 +2243,61 @@
       <c r="T19" s="2">
         <v>80</v>
       </c>
-      <c r="U19" s="15" t="s">
+      <c r="U19" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="V19" s="15" t="s">
+      <c r="V19" s="17" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="8:21">
-      <c r="H20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="9"/>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:21">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="11"/>
       <c r="U20" s="2"/>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C21" s="8">
+      <c r="C21" s="9">
         <v>25</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="9">
         <v>4</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>1</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="9">
         <v>25</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="10">
         <f t="shared" ref="I21:I24" si="0">H21*4</f>
         <v>3.96e+21</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="10">
         <f t="shared" ref="K21:K24" si="1">J21*4</f>
         <v>3.96e+22</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L21" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M21" s="9">
+      <c r="M21" s="10">
         <f t="shared" ref="M21:M24" si="2">L21*4</f>
         <v>3.96e+27</v>
       </c>
@@ -2317,47 +2322,47 @@
       <c r="T21" s="2">
         <v>80</v>
       </c>
-      <c r="U21" s="15" t="s">
+      <c r="U21" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="V21" s="15" t="s">
+      <c r="V21" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C22" s="8">
+      <c r="C22" s="9">
         <v>26</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="9">
         <v>4</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="9">
         <v>26</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="9">
         <v>50</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
         <v>3.96e+23</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="10">
         <f t="shared" si="1"/>
         <v>3.96e+24</v>
       </c>
-      <c r="L22" s="16" t="s">
+      <c r="L22" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M22" s="10">
         <f t="shared" si="2"/>
         <v>3.96e+29</v>
       </c>
@@ -2382,47 +2387,47 @@
       <c r="T22" s="2">
         <v>80</v>
       </c>
-      <c r="U22" s="15" t="s">
+      <c r="U22" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="V22" s="15" t="s">
+      <c r="V22" s="17" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C23" s="8">
+      <c r="C23" s="9">
         <v>27</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <v>4</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>51</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <v>75</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
         <v>3.96e+25</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="10">
         <f t="shared" si="1"/>
         <v>3.96e+26</v>
       </c>
-      <c r="L23" s="16" t="s">
+      <c r="L23" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="10">
         <f t="shared" si="2"/>
         <v>3.96e+31</v>
       </c>
@@ -2447,47 +2452,47 @@
       <c r="T23" s="2">
         <v>80</v>
       </c>
-      <c r="U23" s="15" t="s">
+      <c r="U23" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="V23" s="15" t="s">
+      <c r="V23" s="17" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C24" s="8">
+      <c r="C24" s="9">
         <v>28</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9">
         <v>4</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>76</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="9">
         <v>100</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
         <v>3.96e+27</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J24" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="10">
         <f t="shared" si="1"/>
         <v>3.96e+28</v>
       </c>
-      <c r="L24" s="16" t="s">
+      <c r="L24" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="M24" s="9">
+      <c r="M24" s="10">
         <f t="shared" si="2"/>
         <v>3.96e+33</v>
       </c>
@@ -2512,37 +2517,46 @@
       <c r="T24" s="2">
         <v>80</v>
       </c>
-      <c r="U24" s="15" t="s">
+      <c r="U24" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="V24" s="15" t="s">
+      <c r="V24" s="17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="25" customHeight="1" spans="10:11">
-      <c r="J25" s="9"/>
-      <c r="K25" s="10"/>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
     </row>
     <row r="26" customHeight="1" spans="10:11">
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
     </row>
     <row r="27" customHeight="1" spans="10:11">
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customHeight="1" spans="10:11">
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
     </row>
     <row r="29" customHeight="1" spans="10:12">
-      <c r="J29" s="10"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
     </row>
     <row r="30" customHeight="1" spans="11:12">
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
   <si>
     <t>ID</t>
   </si>
@@ -86,6 +86,9 @@
     <t>MulDamageResist</t>
   </si>
   <si>
+    <t>Protect</t>
+  </si>
+  <si>
     <t>Exp</t>
   </si>
   <si>
@@ -225,6 +228,36 @@
   </si>
   <si>
     <t>400000000000000</t>
+  </si>
+  <si>
+    <t>深渊沙城</t>
+  </si>
+  <si>
+    <t>99000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>99000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>9900000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>9900000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>990000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>990000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>600000000000000</t>
+  </si>
+  <si>
+    <t>99000000000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>800000000000000</t>
   </si>
 </sst>
 </file>
@@ -238,7 +271,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,12 +289,6 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -734,140 +761,139 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -884,16 +910,6 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -904,7 +920,6 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1224,293 +1239,304 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="4.5" style="4" customWidth="1"/>
+    <col min="1" max="1" width="2.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="3" customWidth="1"/>
     <col min="3" max="3" width="3.125" style="1" customWidth="1"/>
     <col min="4" max="5" width="9.875" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="22.875" style="5" customWidth="1"/>
-    <col min="9" max="9" width="24.125" style="5" customWidth="1"/>
-    <col min="10" max="10" width="23.375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="23.625" style="5" customWidth="1"/>
-    <col min="12" max="12" width="30" style="5" customWidth="1"/>
-    <col min="13" max="13" width="26.875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="8.375" style="4" customWidth="1"/>
-    <col min="15" max="15" width="8.875" style="4" customWidth="1"/>
-    <col min="16" max="16" width="6.375" style="4" customWidth="1"/>
-    <col min="17" max="17" width="8" style="4" customWidth="1"/>
-    <col min="18" max="19" width="7.25" style="4" customWidth="1"/>
-    <col min="20" max="20" width="9.75" style="4" customWidth="1"/>
-    <col min="21" max="21" width="12.875" style="4" customWidth="1"/>
-    <col min="22" max="22" width="13.375" style="4" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="4"/>
+    <col min="8" max="8" width="29.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="35.875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="23.375" style="4" customWidth="1"/>
+    <col min="11" max="11" width="23.625" style="4" customWidth="1"/>
+    <col min="12" max="12" width="41" style="4" customWidth="1"/>
+    <col min="13" max="13" width="26.875" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="8.875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="6.375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="8" style="3" customWidth="1"/>
+    <col min="18" max="19" width="7.25" style="3" customWidth="1"/>
+    <col min="20" max="21" width="8.375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="15.5" style="3" customWidth="1"/>
+    <col min="23" max="23" width="13.375" style="3" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A1" s="4"/>
-      <c r="B1" s="4"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="T3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="15" t="s">
+      <c r="U3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="V3" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="7" t="s">
+      <c r="W3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="15" t="s">
+      <c r="U4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="15" t="s">
+      <c r="V4" s="10" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="W4" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="D5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="G5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="H5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="O5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="P5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="S5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="U5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="V5" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C6" s="9">
+      <c r="Q5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="V5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="W5" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="8">
         <v>1</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="8">
         <v>25</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="9">
         <v>165000</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="9">
         <v>30000</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="9">
         <v>33000</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="9">
         <v>6000</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="9">
         <v>16500000</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <v>3000000</v>
       </c>
       <c r="N6" s="2">
@@ -1534,46 +1560,49 @@
       <c r="T6" s="2">
         <v>0</v>
       </c>
-      <c r="U6" s="17" t="s">
+      <c r="U6" s="2">
+        <v>0</v>
+      </c>
+      <c r="V6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C7" s="8">
+        <v>2</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="V6" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C7" s="9">
-        <v>2</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>1</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>26</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="8">
         <v>50</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>11600000</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="10">
+      <c r="I7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="9">
         <v>2320000</v>
       </c>
-      <c r="K7" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="10">
+      <c r="K7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="9">
         <v>1160000000</v>
       </c>
-      <c r="M7" s="18" t="s">
-        <v>28</v>
+      <c r="M7" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="N7" s="2">
         <v>10</v>
@@ -1596,46 +1625,49 @@
       <c r="T7" s="2">
         <v>0</v>
       </c>
-      <c r="U7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="V7" s="17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C8" s="9">
+      <c r="U7" s="2">
+        <v>0</v>
+      </c>
+      <c r="V7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="W7" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C8" s="8">
         <v>3</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="D8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="8">
         <v>1</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>51</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="8">
         <v>75</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="9">
         <v>837025000</v>
       </c>
-      <c r="I8" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="10">
+      <c r="I8" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="9">
         <v>167405000</v>
       </c>
-      <c r="K8" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="10">
+      <c r="K8" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="9">
         <v>83702500000</v>
       </c>
-      <c r="M8" s="18" t="s">
-        <v>32</v>
+      <c r="M8" s="13" t="s">
+        <v>33</v>
       </c>
       <c r="N8" s="2">
         <v>20</v>
@@ -1658,57 +1690,60 @@
       <c r="T8" s="2">
         <v>0</v>
       </c>
-      <c r="U8" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="V8" s="17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C9" s="9">
+      <c r="U8" s="2">
+        <v>0</v>
+      </c>
+      <c r="V8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="D9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="8">
         <v>1</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>76</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="8">
         <v>100</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="9">
         <v>58655700000</v>
       </c>
-      <c r="I9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="10">
+      <c r="I9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="9">
         <v>11731140000</v>
       </c>
-      <c r="K9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="10">
+      <c r="K9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="9">
         <v>16863800000000</v>
       </c>
-      <c r="M9" s="18" t="s">
-        <v>36</v>
+      <c r="M9" s="13" t="s">
+        <v>37</v>
       </c>
       <c r="N9" s="2">
         <v>75</v>
       </c>
-      <c r="O9" s="12">
+      <c r="O9" s="8">
         <v>10</v>
       </c>
-      <c r="P9" s="12">
+      <c r="P9" s="8">
         <v>15</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="8">
         <v>15</v>
       </c>
       <c r="R9" s="2">
@@ -1720,320 +1755,335 @@
       <c r="T9" s="2">
         <v>0</v>
       </c>
-      <c r="U9" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" s="17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:21">
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="U10" s="16"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C11" s="9">
+      <c r="U9" s="2">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="W9" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="V10" s="11"/>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C11" s="8">
         <v>11</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="D11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="8">
         <v>2</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>1</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="8">
         <v>25</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="9">
         <v>70000000000</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="9">
+        <v>35000000000</v>
+      </c>
+      <c r="K11" s="9">
+        <v>1000000000</v>
+      </c>
+      <c r="L11" s="9">
+        <v>1400000000000000</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="2">
+        <v>135</v>
+      </c>
+      <c r="O11" s="2">
+        <v>65</v>
+      </c>
+      <c r="P11" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>100</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2">
+        <v>0</v>
+      </c>
+      <c r="V11" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" s="12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C12" s="8">
+        <v>12</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="J11" s="11">
-        <v>35000000000</v>
-      </c>
-      <c r="K11" s="10">
-        <v>1000000000</v>
-      </c>
-      <c r="L11" s="11">
+      <c r="E12" s="8">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8">
+        <v>26</v>
+      </c>
+      <c r="G12" s="8">
+        <v>50</v>
+      </c>
+      <c r="H12" s="9">
+        <v>400000000000</v>
+      </c>
+      <c r="I12" s="9">
+        <v>30000000000</v>
+      </c>
+      <c r="J12" s="9">
+        <v>80000000000</v>
+      </c>
+      <c r="K12" s="9">
+        <v>6000000000</v>
+      </c>
+      <c r="L12" s="9">
+        <v>8000000000000000</v>
+      </c>
+      <c r="M12" s="9">
+        <v>600000000000000</v>
+      </c>
+      <c r="N12" s="2">
+        <v>160</v>
+      </c>
+      <c r="O12" s="2">
+        <v>90</v>
+      </c>
+      <c r="P12" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>100</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C13" s="8">
+        <v>13</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8">
+        <v>51</v>
+      </c>
+      <c r="G13" s="8">
+        <v>75</v>
+      </c>
+      <c r="H13" s="9">
+        <v>2200000000000</v>
+      </c>
+      <c r="I13" s="9">
+        <v>100000000000</v>
+      </c>
+      <c r="J13" s="9">
+        <v>440000000000</v>
+      </c>
+      <c r="K13" s="9">
+        <v>20000000000</v>
+      </c>
+      <c r="L13" s="9">
+        <v>4.4e+16</v>
+      </c>
+      <c r="M13" s="9">
+        <v>2000000000000000</v>
+      </c>
+      <c r="N13" s="2">
+        <v>185</v>
+      </c>
+      <c r="O13" s="2">
+        <v>115</v>
+      </c>
+      <c r="P13" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>100</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="W13" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C14" s="8">
+        <v>14</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8">
+        <v>76</v>
+      </c>
+      <c r="G14" s="8">
+        <v>100</v>
+      </c>
+      <c r="H14" s="9">
+        <v>12000000000000</v>
+      </c>
+      <c r="I14" s="9">
+        <v>1000000000000</v>
+      </c>
+      <c r="J14" s="9">
+        <v>2400000000000</v>
+      </c>
+      <c r="K14" s="9">
+        <v>200000000000</v>
+      </c>
+      <c r="L14" s="9">
+        <v>2.4e+17</v>
+      </c>
+      <c r="M14" s="9">
+        <v>2e+16</v>
+      </c>
+      <c r="N14" s="2">
+        <v>209</v>
+      </c>
+      <c r="O14" s="2">
+        <v>139</v>
+      </c>
+      <c r="P14" s="2">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>100</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2">
+        <v>0</v>
+      </c>
+      <c r="V14" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="W14" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C16" s="8">
+        <v>21</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1</v>
+      </c>
+      <c r="G16" s="8">
+        <v>25</v>
+      </c>
+      <c r="H16" s="9">
+        <v>70000000000000</v>
+      </c>
+      <c r="I16" s="9">
+        <v>280000000000000</v>
+      </c>
+      <c r="J16" s="9">
+        <v>350000000000000</v>
+      </c>
+      <c r="K16" s="9">
         <v>1400000000000000</v>
       </c>
-      <c r="M11" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="N11" s="3">
-        <v>135</v>
-      </c>
-      <c r="O11" s="3">
-        <v>65</v>
-      </c>
-      <c r="P11" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>100</v>
-      </c>
-      <c r="R11" s="2">
-        <v>0</v>
-      </c>
-      <c r="S11" s="2">
-        <v>0</v>
-      </c>
-      <c r="T11" s="2">
-        <v>0</v>
-      </c>
-      <c r="U11" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="V11" s="17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C12" s="9">
-        <v>12</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="9">
-        <v>2</v>
-      </c>
-      <c r="F12" s="9">
-        <v>26</v>
-      </c>
-      <c r="G12" s="9">
-        <v>50</v>
-      </c>
-      <c r="H12" s="11">
-        <v>400000000000</v>
-      </c>
-      <c r="I12" s="10">
-        <v>30000000000</v>
-      </c>
-      <c r="J12" s="11">
-        <v>80000000000</v>
-      </c>
-      <c r="K12" s="10">
-        <v>6000000000</v>
-      </c>
-      <c r="L12" s="11">
-        <v>8000000000000000</v>
-      </c>
-      <c r="M12" s="10">
-        <v>600000000000000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>160</v>
-      </c>
-      <c r="O12" s="3">
-        <v>90</v>
-      </c>
-      <c r="P12" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
-      </c>
-      <c r="R12" s="2">
-        <v>0</v>
-      </c>
-      <c r="S12" s="2">
-        <v>0</v>
-      </c>
-      <c r="T12" s="2">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="V12" s="17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C13" s="9">
-        <v>13</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="9">
-        <v>2</v>
-      </c>
-      <c r="F13" s="9">
-        <v>51</v>
-      </c>
-      <c r="G13" s="9">
-        <v>75</v>
-      </c>
-      <c r="H13" s="11">
-        <v>2200000000000</v>
-      </c>
-      <c r="I13" s="10">
-        <v>100000000000</v>
-      </c>
-      <c r="J13" s="10">
-        <v>440000000000</v>
-      </c>
-      <c r="K13" s="10">
-        <v>20000000000</v>
-      </c>
-      <c r="L13" s="10">
-        <v>4.4e+16</v>
-      </c>
-      <c r="M13" s="10">
-        <v>2000000000000000</v>
-      </c>
-      <c r="N13" s="3">
-        <v>185</v>
-      </c>
-      <c r="O13" s="3">
-        <v>115</v>
-      </c>
-      <c r="P13" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>100</v>
-      </c>
-      <c r="R13" s="2">
-        <v>0</v>
-      </c>
-      <c r="S13" s="2">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2">
-        <v>0</v>
-      </c>
-      <c r="U13" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="V13" s="17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C14" s="9">
-        <v>14</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="9">
-        <v>2</v>
-      </c>
-      <c r="F14" s="9">
-        <v>76</v>
-      </c>
-      <c r="G14" s="9">
-        <v>100</v>
-      </c>
-      <c r="H14" s="11">
-        <v>12000000000000</v>
-      </c>
-      <c r="I14" s="10">
-        <v>1000000000000</v>
-      </c>
-      <c r="J14" s="10">
-        <v>2400000000000</v>
-      </c>
-      <c r="K14" s="10">
-        <v>200000000000</v>
-      </c>
-      <c r="L14" s="10">
-        <v>2.4e+17</v>
-      </c>
-      <c r="M14" s="10">
-        <v>2e+16</v>
-      </c>
-      <c r="N14" s="3">
-        <v>209</v>
-      </c>
-      <c r="O14" s="3">
-        <v>139</v>
-      </c>
-      <c r="P14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>100</v>
-      </c>
-      <c r="R14" s="2">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2">
-        <v>0</v>
-      </c>
-      <c r="U14" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="V14" s="17" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C16" s="9">
-        <v>21</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="9">
-        <v>3</v>
-      </c>
-      <c r="F16" s="9">
-        <v>1</v>
-      </c>
-      <c r="G16" s="9">
-        <v>25</v>
-      </c>
-      <c r="H16" s="10">
-        <v>70000000000000</v>
-      </c>
-      <c r="I16" s="10">
-        <v>280000000000000</v>
-      </c>
-      <c r="J16" s="10">
-        <v>350000000000000</v>
-      </c>
-      <c r="K16" s="10">
-        <v>1400000000000000</v>
-      </c>
-      <c r="L16" s="10">
+      <c r="L16" s="9">
         <v>1.4e+19</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="9">
         <v>5.6e+19</v>
       </c>
       <c r="N16" s="2">
@@ -2057,45 +2107,48 @@
       <c r="T16" s="2">
         <v>80</v>
       </c>
-      <c r="U16" s="17" t="s">
+      <c r="U16" s="2">
+        <v>0</v>
+      </c>
+      <c r="V16" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="W16" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C17" s="8">
+        <v>22</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="V16" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C17" s="9">
-        <v>22</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>3</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="8">
         <v>26</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="8">
         <v>50</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="9">
         <v>700000000000000</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="9">
         <v>2800000000000000</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="9">
         <v>3500000000000000</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="9">
         <v>1.4e+16</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>1.4e+20</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <v>5.6e+20</v>
       </c>
       <c r="N17" s="2">
@@ -2119,45 +2172,48 @@
       <c r="T17" s="2">
         <v>80</v>
       </c>
-      <c r="U17" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="V17" s="17" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C18" s="9">
+      <c r="U17" s="2">
+        <v>0</v>
+      </c>
+      <c r="V17" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="W17" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C18" s="8">
         <v>23</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="D18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="8">
         <v>3</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="8">
         <v>51</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="8">
         <v>75</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="9">
         <v>7000000000000000</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="9">
         <v>2.8e+16</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="9">
         <v>3.5e+16</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="9">
         <v>1.4e+17</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <v>1.4e+21</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <v>5.6e+21</v>
       </c>
       <c r="N18" s="2">
@@ -2181,45 +2237,48 @@
       <c r="T18" s="2">
         <v>80</v>
       </c>
-      <c r="U18" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="V18" s="17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C19" s="9">
+      <c r="U18" s="2">
+        <v>0</v>
+      </c>
+      <c r="V18" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="W18" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C19" s="8">
         <v>24</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E19" s="9">
+      <c r="D19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="8">
         <v>3</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="8">
         <v>76</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="8">
         <v>100</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="9">
         <v>7e+16</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="9">
         <v>2.8e+17</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="9">
         <v>3.5e+17</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="9">
         <v>1.4e+18</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="9">
         <v>1.4e+22</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>5.6e+22</v>
       </c>
       <c r="N19" s="2">
@@ -2243,61 +2302,63 @@
       <c r="T19" s="2">
         <v>80</v>
       </c>
-      <c r="U19" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="V19" s="17" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="3:21">
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="11"/>
-      <c r="U20" s="2"/>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C21" s="9">
+      <c r="U19" s="2">
+        <v>0</v>
+      </c>
+      <c r="V19" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C21" s="8">
         <v>25</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="9">
+      <c r="D21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="8">
         <v>4</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="8">
         <v>1</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="8">
         <v>25</v>
       </c>
-      <c r="H21" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="10">
+      <c r="H21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="9">
         <f t="shared" ref="I21:I24" si="0">H21*4</f>
         <v>3.96e+21</v>
       </c>
-      <c r="J21" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="K21" s="10">
+      <c r="J21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K21" s="9">
         <f t="shared" ref="K21:K24" si="1">J21*4</f>
         <v>3.96e+22</v>
       </c>
-      <c r="L21" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="M21" s="10">
+      <c r="L21" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="9">
         <f t="shared" ref="M21:M24" si="2">L21*4</f>
         <v>3.96e+27</v>
       </c>
@@ -2322,47 +2383,50 @@
       <c r="T21" s="2">
         <v>80</v>
       </c>
-      <c r="U21" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="V21" s="17" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C22" s="9">
+      <c r="U21" s="2">
+        <v>0</v>
+      </c>
+      <c r="V21" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="W21" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C22" s="8">
         <v>26</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="8">
+        <v>4</v>
+      </c>
+      <c r="F22" s="8">
+        <v>26</v>
+      </c>
+      <c r="G22" s="8">
         <v>50</v>
       </c>
-      <c r="E22" s="9">
-        <v>4</v>
-      </c>
-      <c r="F22" s="9">
-        <v>26</v>
-      </c>
-      <c r="G22" s="9">
-        <v>50</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="I22" s="10">
+      <c r="H22" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="9">
         <f t="shared" si="0"/>
         <v>3.96e+23</v>
       </c>
-      <c r="J22" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" s="10">
+      <c r="J22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K22" s="9">
         <f t="shared" si="1"/>
         <v>3.96e+24</v>
       </c>
-      <c r="L22" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" s="10">
+      <c r="L22" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="M22" s="9">
         <f t="shared" si="2"/>
         <v>3.96e+29</v>
       </c>
@@ -2387,47 +2451,50 @@
       <c r="T22" s="2">
         <v>80</v>
       </c>
-      <c r="U22" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="V22" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C23" s="9">
+      <c r="U22" s="2">
+        <v>0</v>
+      </c>
+      <c r="V22" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="W22" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C23" s="8">
         <v>27</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="9">
+      <c r="D23" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="8">
         <v>4</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="8">
         <v>51</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="8">
         <v>75</v>
       </c>
-      <c r="H23" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="I23" s="10">
+      <c r="H23" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="9">
         <f t="shared" si="0"/>
         <v>3.96e+25</v>
       </c>
-      <c r="J23" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="K23" s="10">
+      <c r="J23" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K23" s="9">
         <f t="shared" si="1"/>
         <v>3.96e+26</v>
       </c>
-      <c r="L23" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="M23" s="10">
+      <c r="L23" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="9">
         <f t="shared" si="2"/>
         <v>3.96e+31</v>
       </c>
@@ -2452,47 +2519,50 @@
       <c r="T23" s="2">
         <v>80</v>
       </c>
-      <c r="U23" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="V23" s="17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C24" s="9">
+      <c r="U23" s="2">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="W23" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C24" s="8">
         <v>28</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="9">
+      <c r="D24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="8">
         <v>4</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="8">
         <v>76</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="8">
         <v>100</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="10">
+      <c r="H24" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I24" s="9">
         <f t="shared" si="0"/>
         <v>3.96e+27</v>
       </c>
-      <c r="J24" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="K24" s="10">
+      <c r="J24" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="K24" s="9">
         <f t="shared" si="1"/>
         <v>3.96e+28</v>
       </c>
-      <c r="L24" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="M24" s="10">
+      <c r="L24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="9">
         <f t="shared" si="2"/>
         <v>3.96e+33</v>
       </c>
@@ -2517,50 +2587,356 @@
       <c r="T24" s="2">
         <v>80</v>
       </c>
-      <c r="U24" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="V24" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-    </row>
-    <row r="26" customHeight="1" spans="10:11">
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-    </row>
-    <row r="27" customHeight="1" spans="10:11">
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-    </row>
-    <row r="28" customHeight="1" spans="10:11">
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-    </row>
-    <row r="29" customHeight="1" spans="10:12">
-      <c r="J29" s="13"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" customHeight="1" spans="11:12">
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
+      <c r="U24" s="2">
+        <v>0</v>
+      </c>
+      <c r="V24" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="W24" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C26" s="8">
+        <v>25</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="8">
+        <v>5</v>
+      </c>
+      <c r="F26" s="8">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8">
+        <v>25</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" ref="I26:M26" si="3">H26*4</f>
+        <v>3.96e+35</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" si="3"/>
+        <v>3.96e+35</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="3"/>
+        <v>3.96e+41</v>
+      </c>
+      <c r="N26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="O26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="P26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>1500</v>
+      </c>
+      <c r="R26" s="2">
+        <v>80</v>
+      </c>
+      <c r="S26" s="2">
+        <v>80</v>
+      </c>
+      <c r="T26" s="2">
+        <v>99</v>
+      </c>
+      <c r="U26" s="2">
+        <v>90</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C27" s="8">
+        <v>26</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="8">
+        <v>5</v>
+      </c>
+      <c r="F27" s="8">
+        <v>26</v>
+      </c>
+      <c r="G27" s="8">
+        <v>50</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" ref="I27:M27" si="4">H27*4</f>
+        <v>3.96e+37</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="4"/>
+        <v>3.96e+37</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="4"/>
+        <v>3.96e+43</v>
+      </c>
+      <c r="N27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="O27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="P27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>1800</v>
+      </c>
+      <c r="R27" s="2">
+        <v>80</v>
+      </c>
+      <c r="S27" s="2">
+        <v>80</v>
+      </c>
+      <c r="T27" s="2">
+        <v>99</v>
+      </c>
+      <c r="U27" s="2">
+        <v>90</v>
+      </c>
+      <c r="V27" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C28" s="8">
+        <v>27</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="8">
+        <v>5</v>
+      </c>
+      <c r="F28" s="8">
+        <v>51</v>
+      </c>
+      <c r="G28" s="8">
+        <v>75</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" ref="I28:M28" si="5">H28*4</f>
+        <v>3.96e+39</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" si="5"/>
+        <v>3.96e+39</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="5"/>
+        <v>3.96e+45</v>
+      </c>
+      <c r="N28" s="2">
+        <v>2100</v>
+      </c>
+      <c r="O28" s="2">
+        <v>2100</v>
+      </c>
+      <c r="P28" s="2">
+        <v>2100</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>2100</v>
+      </c>
+      <c r="R28" s="2">
+        <v>80</v>
+      </c>
+      <c r="S28" s="2">
+        <v>80</v>
+      </c>
+      <c r="T28" s="2">
+        <v>99</v>
+      </c>
+      <c r="U28" s="2">
+        <v>90</v>
+      </c>
+      <c r="V28" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="W28" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C29" s="8">
+        <v>28</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="8">
+        <v>5</v>
+      </c>
+      <c r="F29" s="8">
+        <v>76</v>
+      </c>
+      <c r="G29" s="8">
+        <v>100</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" ref="I29:M29" si="6">H29*4</f>
+        <v>3.96e+41</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K29" s="9">
+        <f t="shared" si="6"/>
+        <v>3.96e+41</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="M29" s="9">
+        <f t="shared" si="6"/>
+        <v>3.96e+47</v>
+      </c>
+      <c r="N29" s="2">
+        <v>2400</v>
+      </c>
+      <c r="O29" s="2">
+        <v>2400</v>
+      </c>
+      <c r="P29" s="2">
+        <v>2400</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>2400</v>
+      </c>
+      <c r="R29" s="2">
+        <v>80</v>
+      </c>
+      <c r="S29" s="2">
+        <v>80</v>
+      </c>
+      <c r="T29" s="2">
+        <v>99</v>
+      </c>
+      <c r="U29" s="2">
+        <v>90</v>
+      </c>
+      <c r="V29" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="W29" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+    </row>
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:M3 G4:M4 G5:R5 F4:F5 C3:E5 N3:R4 S3:T5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:M3 U3 G4:M4 U4 G5:R5 U5 F4:F5 N3:R4 C3:E5 S3:T5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C26" s="8">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>66</v>
@@ -2680,7 +2680,7 @@
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C27" s="8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>66</v>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C28" s="8">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>66</v>
@@ -2816,7 +2816,7 @@
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C29" s="8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>66</v>
@@ -2936,7 +2936,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:M3 U3 G4:M4 U4 G5:R5 U5 F4:F5 N3:R4 C3:E5 S3:T5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:M3 G4:M4 G5:R5 F4:F5 N3:R4 C3:E5 S3:U5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
   <si>
     <t>ID</t>
   </si>
@@ -110,93 +110,69 @@
     <t>普通沙城</t>
   </si>
   <si>
+    <t>1.18</t>
+  </si>
+  <si>
     <t>100000000000</t>
   </si>
   <si>
-    <t>1675000</t>
-  </si>
-  <si>
-    <t>335000</t>
-  </si>
-  <si>
-    <t>167500000</t>
-  </si>
-  <si>
     <t>200000000000</t>
   </si>
   <si>
-    <t>141400000</t>
-  </si>
-  <si>
-    <t>28280000</t>
-  </si>
-  <si>
-    <t>14140000000</t>
-  </si>
-  <si>
     <t>300000000000</t>
   </si>
   <si>
-    <t>8476600000</t>
-  </si>
-  <si>
-    <t>1695320000</t>
-  </si>
-  <si>
-    <t>5000000000000</t>
-  </si>
-  <si>
     <t>400000000000</t>
   </si>
   <si>
     <t>困难沙城</t>
   </si>
   <si>
-    <t>5000000000</t>
+    <t>1000000000000</t>
+  </si>
+  <si>
+    <t>2000000000000</t>
+  </si>
+  <si>
+    <t>3000000000000</t>
+  </si>
+  <si>
+    <t>4000000000000</t>
+  </si>
+  <si>
+    <t>噩梦沙城</t>
+  </si>
+  <si>
+    <t>10000000000000</t>
+  </si>
+  <si>
+    <t>20000000000000</t>
+  </si>
+  <si>
+    <t>30000000000000</t>
+  </si>
+  <si>
+    <t>40000000000000</t>
+  </si>
+  <si>
+    <t>地狱沙城</t>
+  </si>
+  <si>
+    <t>990000000000000000000</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>9900000000000000000000</t>
+  </si>
+  <si>
+    <t>990000000000000000000000000</t>
   </si>
   <si>
     <t>100000000000000</t>
   </si>
   <si>
-    <t>1000000000000</t>
-  </si>
-  <si>
-    <t>2000000000000</t>
-  </si>
-  <si>
-    <t>3000000000000</t>
-  </si>
-  <si>
-    <t>4000000000000</t>
-  </si>
-  <si>
-    <t>噩梦沙城</t>
-  </si>
-  <si>
-    <t>10000000000000</t>
-  </si>
-  <si>
-    <t>20000000000000</t>
-  </si>
-  <si>
-    <t>30000000000000</t>
-  </si>
-  <si>
-    <t>40000000000000</t>
-  </si>
-  <si>
-    <t>地狱沙城</t>
-  </si>
-  <si>
-    <t>990000000000000000000</t>
-  </si>
-  <si>
-    <t>9900000000000000000000</t>
-  </si>
-  <si>
-    <t>990000000000000000000000000</t>
-  </si>
-  <si>
     <t>99000000000000000000000</t>
   </si>
   <si>
@@ -233,31 +209,10 @@
     <t>深渊沙城</t>
   </si>
   <si>
-    <t>99000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>99000000000000000000000000000000000000000</t>
+    <t>99000000000000000000000000000000</t>
   </si>
   <si>
     <t>9900000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>9900000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>990000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>990000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>600000000000000</t>
-  </si>
-  <si>
-    <t>99000000000000000000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>800000000000000</t>
   </si>
 </sst>
 </file>
@@ -916,10 +871,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1239,7 +1194,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W33"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.875" style="3" customWidth="1"/>
@@ -1247,12 +1202,12 @@
     <col min="3" max="3" width="3.125" style="1" customWidth="1"/>
     <col min="4" max="5" width="9.875" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="35.875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="23.375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="23.625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="4" customWidth="1"/>
+    <col min="10" max="10" width="38.75" style="4" customWidth="1"/>
+    <col min="11" max="11" width="4.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="41" style="4" customWidth="1"/>
-    <col min="13" max="13" width="26.875" style="4" customWidth="1"/>
+    <col min="13" max="13" width="6" style="4" customWidth="1"/>
     <col min="14" max="14" width="8.375" style="3" customWidth="1"/>
     <col min="15" max="15" width="8.875" style="3" customWidth="1"/>
     <col min="16" max="16" width="6.375" style="3" customWidth="1"/>
@@ -1460,19 +1415,19 @@
         <v>23</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>23</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>22</v>
@@ -1524,20 +1479,20 @@
       <c r="H6" s="9">
         <v>165000</v>
       </c>
-      <c r="I6" s="9">
-        <v>30000</v>
+      <c r="I6" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J6" s="9">
         <v>33000</v>
       </c>
-      <c r="K6" s="9">
-        <v>6000</v>
+      <c r="K6" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L6" s="9">
         <v>16500000</v>
       </c>
-      <c r="M6" s="9">
-        <v>3000000</v>
+      <c r="M6" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N6" s="2">
         <v>0</v>
@@ -1563,11 +1518,11 @@
       <c r="U6" s="2">
         <v>0</v>
       </c>
-      <c r="V6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="W6" s="12" t="s">
-        <v>26</v>
+      <c r="V6" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -1589,20 +1544,20 @@
       <c r="H7" s="9">
         <v>11600000</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>27</v>
+      <c r="I7" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J7" s="9">
         <v>2320000</v>
       </c>
-      <c r="K7" s="13" t="s">
-        <v>28</v>
+      <c r="K7" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L7" s="9">
         <v>1160000000</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>29</v>
+      <c r="M7" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N7" s="2">
         <v>10</v>
@@ -1628,11 +1583,11 @@
       <c r="U7" s="2">
         <v>0</v>
       </c>
-      <c r="V7" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="W7" s="12" t="s">
-        <v>30</v>
+      <c r="V7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="13" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -1654,20 +1609,20 @@
       <c r="H8" s="9">
         <v>837025000</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>31</v>
+      <c r="I8" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J8" s="9">
         <v>167405000</v>
       </c>
-      <c r="K8" s="13" t="s">
-        <v>32</v>
+      <c r="K8" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L8" s="9">
         <v>83702500000</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>33</v>
+      <c r="M8" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N8" s="2">
         <v>20</v>
@@ -1693,11 +1648,11 @@
       <c r="U8" s="2">
         <v>0</v>
       </c>
-      <c r="V8" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="W8" s="12" t="s">
-        <v>34</v>
+      <c r="V8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -1720,19 +1675,19 @@
         <v>58655700000</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="J9" s="9">
         <v>11731140000</v>
       </c>
-      <c r="K9" s="13" t="s">
-        <v>36</v>
+      <c r="K9" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L9" s="9">
         <v>16863800000000</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>37</v>
+      <c r="M9" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N9" s="2">
         <v>75</v>
@@ -1758,11 +1713,11 @@
       <c r="U9" s="2">
         <v>0</v>
       </c>
-      <c r="V9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="W9" s="12" t="s">
-        <v>38</v>
+      <c r="V9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:22">
@@ -1784,7 +1739,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E11" s="8">
         <v>2</v>
@@ -1799,19 +1754,19 @@
         <v>70000000000</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="J11" s="9">
         <v>35000000000</v>
       </c>
-      <c r="K11" s="9">
-        <v>1000000000</v>
+      <c r="K11" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L11" s="9">
         <v>1400000000000000</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>41</v>
+      <c r="M11" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N11" s="2">
         <v>135</v>
@@ -1837,11 +1792,11 @@
       <c r="U11" s="2">
         <v>0</v>
       </c>
-      <c r="V11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="W11" s="12" t="s">
-        <v>42</v>
+      <c r="V11" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="W11" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -1849,7 +1804,7 @@
         <v>12</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E12" s="8">
         <v>2</v>
@@ -1863,20 +1818,20 @@
       <c r="H12" s="9">
         <v>400000000000</v>
       </c>
-      <c r="I12" s="9">
-        <v>30000000000</v>
+      <c r="I12" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J12" s="9">
         <v>80000000000</v>
       </c>
-      <c r="K12" s="9">
-        <v>6000000000</v>
+      <c r="K12" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L12" s="9">
         <v>8000000000000000</v>
       </c>
-      <c r="M12" s="9">
-        <v>600000000000000</v>
+      <c r="M12" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N12" s="2">
         <v>160</v>
@@ -1902,11 +1857,11 @@
       <c r="U12" s="2">
         <v>0</v>
       </c>
-      <c r="V12" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="W12" s="12" t="s">
-        <v>43</v>
+      <c r="V12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -1914,7 +1869,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E13" s="8">
         <v>2</v>
@@ -1928,20 +1883,20 @@
       <c r="H13" s="9">
         <v>2200000000000</v>
       </c>
-      <c r="I13" s="9">
-        <v>100000000000</v>
+      <c r="I13" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J13" s="9">
         <v>440000000000</v>
       </c>
-      <c r="K13" s="9">
-        <v>20000000000</v>
+      <c r="K13" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L13" s="9">
         <v>4.4e+16</v>
       </c>
-      <c r="M13" s="9">
-        <v>2000000000000000</v>
+      <c r="M13" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N13" s="2">
         <v>185</v>
@@ -1967,11 +1922,11 @@
       <c r="U13" s="2">
         <v>0</v>
       </c>
-      <c r="V13" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="W13" s="12" t="s">
-        <v>44</v>
+      <c r="V13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="W13" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -1979,7 +1934,7 @@
         <v>14</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E14" s="8">
         <v>2</v>
@@ -1993,20 +1948,20 @@
       <c r="H14" s="9">
         <v>12000000000000</v>
       </c>
-      <c r="I14" s="9">
-        <v>1000000000000</v>
+      <c r="I14" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J14" s="9">
         <v>2400000000000</v>
       </c>
-      <c r="K14" s="9">
-        <v>200000000000</v>
+      <c r="K14" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L14" s="9">
         <v>2.4e+17</v>
       </c>
-      <c r="M14" s="9">
-        <v>2e+16</v>
+      <c r="M14" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N14" s="2">
         <v>209</v>
@@ -2032,11 +1987,11 @@
       <c r="U14" s="2">
         <v>0</v>
       </c>
-      <c r="V14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="W14" s="12" t="s">
-        <v>45</v>
+      <c r="V14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" s="13" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
@@ -2057,7 +2012,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E16" s="8">
         <v>3</v>
@@ -2071,20 +2026,20 @@
       <c r="H16" s="9">
         <v>70000000000000</v>
       </c>
-      <c r="I16" s="9">
-        <v>280000000000000</v>
+      <c r="I16" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J16" s="9">
         <v>350000000000000</v>
       </c>
-      <c r="K16" s="9">
-        <v>1400000000000000</v>
+      <c r="K16" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L16" s="9">
         <v>1.4e+19</v>
       </c>
-      <c r="M16" s="9">
-        <v>5.6e+19</v>
+      <c r="M16" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N16" s="2">
         <v>250</v>
@@ -2110,11 +2065,11 @@
       <c r="U16" s="2">
         <v>0</v>
       </c>
-      <c r="V16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="W16" s="12" t="s">
-        <v>47</v>
+      <c r="V16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="W16" s="13" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -2122,7 +2077,7 @@
         <v>22</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E17" s="8">
         <v>3</v>
@@ -2136,20 +2091,20 @@
       <c r="H17" s="9">
         <v>700000000000000</v>
       </c>
-      <c r="I17" s="9">
-        <v>2800000000000000</v>
+      <c r="I17" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J17" s="9">
         <v>3500000000000000</v>
       </c>
-      <c r="K17" s="9">
-        <v>1.4e+16</v>
+      <c r="K17" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L17" s="9">
         <v>1.4e+20</v>
       </c>
-      <c r="M17" s="9">
-        <v>5.6e+20</v>
+      <c r="M17" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N17" s="2">
         <v>300</v>
@@ -2175,11 +2130,11 @@
       <c r="U17" s="2">
         <v>0</v>
       </c>
-      <c r="V17" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="W17" s="12" t="s">
-        <v>48</v>
+      <c r="V17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="W17" s="13" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -2187,7 +2142,7 @@
         <v>23</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E18" s="8">
         <v>3</v>
@@ -2201,20 +2156,20 @@
       <c r="H18" s="9">
         <v>7000000000000000</v>
       </c>
-      <c r="I18" s="9">
-        <v>2.8e+16</v>
+      <c r="I18" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J18" s="9">
         <v>3.5e+16</v>
       </c>
-      <c r="K18" s="9">
-        <v>1.4e+17</v>
+      <c r="K18" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L18" s="9">
         <v>1.4e+21</v>
       </c>
-      <c r="M18" s="9">
-        <v>5.6e+21</v>
+      <c r="M18" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N18" s="2">
         <v>350</v>
@@ -2240,11 +2195,11 @@
       <c r="U18" s="2">
         <v>0</v>
       </c>
-      <c r="V18" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="W18" s="12" t="s">
-        <v>49</v>
+      <c r="V18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="W18" s="13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -2252,7 +2207,7 @@
         <v>24</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E19" s="8">
         <v>3</v>
@@ -2266,20 +2221,20 @@
       <c r="H19" s="9">
         <v>7e+16</v>
       </c>
-      <c r="I19" s="9">
-        <v>2.8e+17</v>
+      <c r="I19" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="J19" s="9">
         <v>3.5e+17</v>
       </c>
-      <c r="K19" s="9">
-        <v>1.4e+18</v>
+      <c r="K19" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="L19" s="9">
         <v>1.4e+22</v>
       </c>
-      <c r="M19" s="9">
-        <v>5.6e+22</v>
+      <c r="M19" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="N19" s="2">
         <v>400</v>
@@ -2305,11 +2260,11 @@
       <c r="U19" s="2">
         <v>0</v>
       </c>
-      <c r="V19" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>50</v>
+      <c r="V19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="W19" s="13" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
@@ -2330,7 +2285,7 @@
         <v>25</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E21" s="8">
         <v>4</v>
@@ -2341,26 +2296,23 @@
       <c r="G21" s="8">
         <v>25</v>
       </c>
-      <c r="H21" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" ref="I21:I24" si="0">H21*4</f>
-        <v>3.96e+21</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" ref="K21:K24" si="1">J21*4</f>
-        <v>3.96e+22</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="M21" s="9">
-        <f t="shared" ref="M21:M24" si="2">L21*4</f>
-        <v>3.96e+27</v>
+      <c r="H21" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M21" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="N21" s="2">
         <v>600</v>
@@ -2386,11 +2338,11 @@
       <c r="U21" s="2">
         <v>0</v>
       </c>
-      <c r="V21" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="W21" s="12" t="s">
-        <v>41</v>
+      <c r="V21" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W21" s="13" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -2398,7 +2350,7 @@
         <v>26</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E22" s="8">
         <v>4</v>
@@ -2409,26 +2361,23 @@
       <c r="G22" s="8">
         <v>50</v>
       </c>
-      <c r="H22" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="9">
-        <f t="shared" si="0"/>
-        <v>3.96e+23</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="9">
-        <f t="shared" si="1"/>
-        <v>3.96e+24</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="2"/>
-        <v>3.96e+29</v>
+      <c r="H22" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M22" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="N22" s="2">
         <v>700</v>
@@ -2454,11 +2403,11 @@
       <c r="U22" s="2">
         <v>0</v>
       </c>
-      <c r="V22" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="W22" s="12" t="s">
-        <v>58</v>
+      <c r="V22" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="W22" s="13" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -2466,7 +2415,7 @@
         <v>27</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E23" s="8">
         <v>4</v>
@@ -2477,26 +2426,23 @@
       <c r="G23" s="8">
         <v>75</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="0"/>
-        <v>3.96e+25</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" si="1"/>
-        <v>3.96e+26</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="M23" s="9">
-        <f t="shared" si="2"/>
-        <v>3.96e+31</v>
+      <c r="H23" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="N23" s="2">
         <v>800</v>
@@ -2522,11 +2468,11 @@
       <c r="U23" s="2">
         <v>0</v>
       </c>
-      <c r="V23" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>62</v>
+      <c r="V23" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="W23" s="13" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:23">
@@ -2534,7 +2480,7 @@
         <v>28</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E24" s="8">
         <v>4</v>
@@ -2545,26 +2491,23 @@
       <c r="G24" s="8">
         <v>100</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="9">
-        <f t="shared" si="0"/>
-        <v>3.96e+27</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="K24" s="9">
-        <f t="shared" si="1"/>
-        <v>3.96e+28</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="M24" s="9">
-        <f t="shared" si="2"/>
-        <v>3.96e+33</v>
+      <c r="H24" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="N24" s="2">
         <v>900</v>
@@ -2590,11 +2533,11 @@
       <c r="U24" s="2">
         <v>0</v>
       </c>
-      <c r="V24" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="W24" s="12" t="s">
-        <v>65</v>
+      <c r="V24" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="W24" s="13" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
@@ -2615,7 +2558,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E26" s="8">
         <v>5</v>
@@ -2624,40 +2567,37 @@
         <v>1</v>
       </c>
       <c r="G26" s="8">
-        <v>25</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>67</v>
+        <v>100</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" ref="I26:M26" si="3">H26*4</f>
-        <v>3.96e+35</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="3"/>
-        <v>3.96e+35</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>68</v>
+        <v>2</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="3"/>
-        <v>3.96e+41</v>
+        <v>2</v>
       </c>
       <c r="N26" s="2">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="O26" s="2">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="P26" s="2">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="Q26" s="2">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="R26" s="2">
         <v>80</v>
@@ -2671,216 +2611,51 @@
       <c r="U26" s="2">
         <v>90</v>
       </c>
-      <c r="V26" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C27" s="8">
-        <v>30</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="8">
-        <v>5</v>
-      </c>
-      <c r="F27" s="8">
-        <v>26</v>
-      </c>
-      <c r="G27" s="8">
+      <c r="V26" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" ref="I27:M27" si="4">H27*4</f>
-        <v>3.96e+37</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="K27" s="9">
-        <f t="shared" si="4"/>
-        <v>3.96e+37</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="M27" s="9">
-        <f t="shared" si="4"/>
-        <v>3.96e+43</v>
-      </c>
-      <c r="N27" s="2">
-        <v>1800</v>
-      </c>
-      <c r="O27" s="2">
-        <v>1800</v>
-      </c>
-      <c r="P27" s="2">
-        <v>1800</v>
-      </c>
-      <c r="Q27" s="2">
-        <v>1800</v>
-      </c>
-      <c r="R27" s="2">
-        <v>80</v>
-      </c>
-      <c r="S27" s="2">
-        <v>80</v>
-      </c>
-      <c r="T27" s="2">
-        <v>99</v>
-      </c>
-      <c r="U27" s="2">
-        <v>90</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C28" s="8">
-        <v>31</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5</v>
-      </c>
-      <c r="F28" s="8">
-        <v>51</v>
-      </c>
-      <c r="G28" s="8">
-        <v>75</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="I28" s="9">
-        <f t="shared" ref="I28:M28" si="5">H28*4</f>
-        <v>3.96e+39</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="K28" s="9">
-        <f t="shared" si="5"/>
-        <v>3.96e+39</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="M28" s="9">
-        <f t="shared" si="5"/>
-        <v>3.96e+45</v>
-      </c>
-      <c r="N28" s="2">
-        <v>2100</v>
-      </c>
-      <c r="O28" s="2">
-        <v>2100</v>
-      </c>
-      <c r="P28" s="2">
-        <v>2100</v>
-      </c>
-      <c r="Q28" s="2">
-        <v>2100</v>
-      </c>
-      <c r="R28" s="2">
-        <v>80</v>
-      </c>
-      <c r="S28" s="2">
-        <v>80</v>
-      </c>
-      <c r="T28" s="2">
-        <v>99</v>
-      </c>
-      <c r="U28" s="2">
-        <v>90</v>
-      </c>
-      <c r="V28" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="W28" s="12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C29" s="8">
-        <v>32</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E29" s="8">
-        <v>5</v>
-      </c>
-      <c r="F29" s="8">
-        <v>76</v>
-      </c>
-      <c r="G29" s="8">
-        <v>100</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="I29" s="9">
-        <f t="shared" ref="I29:M29" si="6">H29*4</f>
-        <v>3.96e+41</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="K29" s="9">
-        <f t="shared" si="6"/>
-        <v>3.96e+41</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="M29" s="9">
-        <f t="shared" si="6"/>
-        <v>3.96e+47</v>
-      </c>
-      <c r="N29" s="2">
-        <v>2400</v>
-      </c>
-      <c r="O29" s="2">
-        <v>2400</v>
-      </c>
-      <c r="P29" s="2">
-        <v>2400</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>2400</v>
-      </c>
-      <c r="R29" s="2">
-        <v>80</v>
-      </c>
-      <c r="S29" s="2">
-        <v>80</v>
-      </c>
-      <c r="T29" s="2">
-        <v>99</v>
-      </c>
-      <c r="U29" s="2">
-        <v>90</v>
-      </c>
-      <c r="V29" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="W29" s="12" t="s">
-        <v>75</v>
-      </c>
+      <c r="W26" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="8"/>
@@ -2895,48 +2670,9 @@
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:M3 G4:M4 G5:R5 F4:F5 N3:R4 C3:E5 S3:U5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3:M3 G4:M4 G5:R5 F4:F5 C3:E5 N3:R4 S3:U5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -1451,7 +1451,7 @@
         <v>22</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V5" s="10" t="s">
         <v>24</v>
@@ -2609,7 +2609,7 @@
         <v>99</v>
       </c>
       <c r="U26" s="2">
-        <v>90</v>
+        <v>99.9</v>
       </c>
       <c r="V26" s="13" t="s">
         <v>50</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -212,7 +212,7 @@
     <t>99000000000000000000000000000000</t>
   </si>
   <si>
-    <t>9900000000000000000000000000000000000</t>
+    <t>990000000000000000000000000000000000000000</t>
   </si>
 </sst>
 </file>
@@ -2600,7 +2600,7 @@
         <v>5000</v>
       </c>
       <c r="R26" s="2">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="S26" s="2">
         <v>80</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="62">
   <si>
     <t>ID</t>
   </si>
@@ -209,10 +209,13 @@
     <t>深渊沙城</t>
   </si>
   <si>
-    <t>99000000000000000000000000000000</t>
-  </si>
-  <si>
-    <t>990000000000000000000000000000000000000000</t>
+    <t>990000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>5990000000000000000000000000000000000000000</t>
+  </si>
+  <si>
+    <t>1.9</t>
   </si>
 </sst>
 </file>
@@ -2584,8 +2587,8 @@
       <c r="L26" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="9">
-        <v>2</v>
+      <c r="M26" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="N26" s="2">
         <v>5000</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>double</t>
   </si>
   <si>
-    <t>普通沙城</t>
+    <t>普通锤兵</t>
   </si>
   <si>
     <t>1.18</t>
@@ -125,7 +125,7 @@
     <t>400000000000</t>
   </si>
   <si>
-    <t>困难沙城</t>
+    <t>困难锤兵</t>
   </si>
   <si>
     <t>1000000000000</t>
@@ -140,7 +140,7 @@
     <t>4000000000000</t>
   </si>
   <si>
-    <t>噩梦沙城</t>
+    <t>噩梦锤兵</t>
   </si>
   <si>
     <t>10000000000000</t>
@@ -155,7 +155,7 @@
     <t>40000000000000</t>
   </si>
   <si>
-    <t>地狱沙城</t>
+    <t>地狱锤兵</t>
   </si>
   <si>
     <t>990000000000000000000</t>
@@ -206,7 +206,7 @@
     <t>400000000000000</t>
   </si>
   <si>
-    <t>深渊沙城</t>
+    <t>深渊锤兵</t>
   </si>
   <si>
     <t>990000000000000000000000000000</t>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -216,6 +216,15 @@
   </si>
   <si>
     <t>1.9</t>
+  </si>
+  <si>
+    <t>永夜锤兵</t>
+  </si>
+  <si>
+    <t>9999那</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
 </sst>
 </file>
@@ -849,7 +858,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -857,6 +866,9 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -872,6 +884,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
@@ -1206,7 +1221,7 @@
     <col min="4" max="5" width="9.875" style="1" customWidth="1"/>
     <col min="6" max="7" width="11.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="41.625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="4" customWidth="1"/>
+    <col min="9" max="9" width="9.375" style="5" customWidth="1"/>
     <col min="10" max="10" width="38.75" style="4" customWidth="1"/>
     <col min="11" max="11" width="4.875" style="4" customWidth="1"/>
     <col min="12" max="12" width="41" style="4" customWidth="1"/>
@@ -1225,12 +1240,12 @@
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -1245,12 +1260,12 @@
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -1265,236 +1280,236 @@
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="10" t="s">
+      <c r="V3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="10" t="s">
+      <c r="W3" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="6" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="S4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="6" t="s">
+      <c r="T4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="6" t="s">
+      <c r="U4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="10" t="s">
+      <c r="V4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="W4" s="10" t="s">
+      <c r="W4" s="11" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="S5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="T5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="U5" s="6" t="s">
+      <c r="U5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="V5" s="10" t="s">
+      <c r="V5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="W5" s="10" t="s">
+      <c r="W5" s="11" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="9">
         <v>25</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>165000</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="9">
+      <c r="I6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="10">
         <v>33000</v>
       </c>
-      <c r="K6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="9">
+      <c r="K6" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" s="10">
         <v>16500000</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N6" s="2">
@@ -1521,45 +1536,45 @@
       <c r="U6" s="2">
         <v>0</v>
       </c>
-      <c r="V6" s="13" t="s">
+      <c r="V6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="W6" s="13" t="s">
+      <c r="W6" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <v>2</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7" s="8">
-        <v>26</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="F7" s="9">
+        <v>26</v>
+      </c>
+      <c r="G7" s="9">
         <v>50</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <v>11600000</v>
       </c>
-      <c r="I7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="9">
+      <c r="I7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="10">
         <v>2320000</v>
       </c>
-      <c r="K7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="9">
+      <c r="K7" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="10">
         <v>1160000000</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N7" s="2">
@@ -1586,45 +1601,45 @@
       <c r="U7" s="2">
         <v>0</v>
       </c>
-      <c r="V7" s="13" t="s">
+      <c r="V7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="W7" s="13" t="s">
+      <c r="W7" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C8" s="8">
+      <c r="C8" s="9">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>1</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>51</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="9">
         <v>75</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <v>837025000</v>
       </c>
-      <c r="I8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="9">
+      <c r="I8" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="10">
         <v>167405000</v>
       </c>
-      <c r="K8" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="9">
+      <c r="K8" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="10">
         <v>83702500000</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N8" s="2">
@@ -1651,57 +1666,57 @@
       <c r="U8" s="2">
         <v>0</v>
       </c>
-      <c r="V8" s="13" t="s">
+      <c r="V8" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="W8" s="13" t="s">
+      <c r="W8" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <v>4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>76</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="9">
         <v>100</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <v>58655700000</v>
       </c>
-      <c r="I9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="9">
+      <c r="I9" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="10">
         <v>11731140000</v>
       </c>
-      <c r="K9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="9">
+      <c r="K9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="10">
         <v>16863800000000</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="M9" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N9" s="2">
         <v>75</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <v>10</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="9">
         <v>15</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="9">
         <v>15</v>
       </c>
       <c r="R9" s="2">
@@ -1716,59 +1731,59 @@
       <c r="U9" s="2">
         <v>0</v>
       </c>
-      <c r="V9" s="13" t="s">
+      <c r="V9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="W9" s="13" t="s">
+      <c r="W9" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="V10" s="11"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="V10" s="12"/>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <v>11</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="9">
         <v>2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>1</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="9">
         <v>25</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="10">
         <v>70000000000</v>
       </c>
-      <c r="I11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="9">
+      <c r="I11" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="10">
         <v>35000000000</v>
       </c>
-      <c r="K11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="9">
+      <c r="K11" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="10">
         <v>1400000000000000</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="2">
@@ -1795,45 +1810,45 @@
       <c r="U11" s="2">
         <v>0</v>
       </c>
-      <c r="V11" s="13" t="s">
+      <c r="V11" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="W11" s="13" t="s">
+      <c r="W11" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C12" s="8">
+      <c r="C12" s="9">
         <v>12</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="9">
         <v>2</v>
       </c>
-      <c r="F12" s="8">
-        <v>26</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="F12" s="9">
+        <v>26</v>
+      </c>
+      <c r="G12" s="9">
         <v>50</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="10">
         <v>400000000000</v>
       </c>
-      <c r="I12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="9">
+      <c r="I12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="10">
         <v>80000000000</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="K12" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" s="10">
         <v>8000000000000000</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="2">
@@ -1860,45 +1875,45 @@
       <c r="U12" s="2">
         <v>0</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="V12" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="W12" s="13" t="s">
+      <c r="W12" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C13" s="8">
+      <c r="C13" s="9">
         <v>13</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="9">
         <v>2</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="9">
         <v>51</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="9">
         <v>75</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="10">
         <v>2200000000000</v>
       </c>
-      <c r="I13" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="9">
+      <c r="I13" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="10">
         <v>440000000000</v>
       </c>
-      <c r="K13" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="K13" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="10">
         <v>4.4e+16</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N13" s="2">
@@ -1925,45 +1940,45 @@
       <c r="U13" s="2">
         <v>0</v>
       </c>
-      <c r="V13" s="13" t="s">
+      <c r="V13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="W13" s="13" t="s">
+      <c r="W13" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <v>14</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <v>2</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <v>76</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <v>100</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="10">
         <v>12000000000000</v>
       </c>
-      <c r="I14" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="9">
+      <c r="I14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="10">
         <v>2400000000000</v>
       </c>
-      <c r="K14" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="9">
+      <c r="K14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="10">
         <v>2.4e+17</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N14" s="2">
@@ -1990,58 +2005,58 @@
       <c r="U14" s="2">
         <v>0</v>
       </c>
-      <c r="V14" s="13" t="s">
+      <c r="V14" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="W14" s="13" t="s">
+      <c r="W14" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C16" s="8">
+      <c r="C16" s="9">
         <v>21</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9">
         <v>3</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="9">
         <v>1</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="9">
         <v>25</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="10">
         <v>70000000000000</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="9">
+      <c r="I16" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J16" s="10">
         <v>350000000000000</v>
       </c>
-      <c r="K16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="9">
+      <c r="K16" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" s="10">
         <v>1.4e+19</v>
       </c>
-      <c r="M16" s="12" t="s">
+      <c r="M16" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="2">
@@ -2068,45 +2083,45 @@
       <c r="U16" s="2">
         <v>0</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="V16" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="W16" s="13" t="s">
+      <c r="W16" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C17" s="8">
+      <c r="C17" s="9">
         <v>22</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="9">
         <v>3</v>
       </c>
-      <c r="F17" s="8">
-        <v>26</v>
-      </c>
-      <c r="G17" s="8">
+      <c r="F17" s="9">
+        <v>26</v>
+      </c>
+      <c r="G17" s="9">
         <v>50</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="10">
         <v>700000000000000</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="9">
+      <c r="I17" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="10">
         <v>3500000000000000</v>
       </c>
-      <c r="K17" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="9">
+      <c r="K17" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="10">
         <v>1.4e+20</v>
       </c>
-      <c r="M17" s="12" t="s">
+      <c r="M17" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N17" s="2">
@@ -2133,45 +2148,45 @@
       <c r="U17" s="2">
         <v>0</v>
       </c>
-      <c r="V17" s="13" t="s">
+      <c r="V17" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="W17" s="13" t="s">
+      <c r="W17" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <v>23</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <v>3</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>51</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="9">
         <v>75</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <v>7000000000000000</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="9">
+      <c r="I18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="10">
         <v>3.5e+16</v>
       </c>
-      <c r="K18" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="9">
+      <c r="K18" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="10">
         <v>1.4e+21</v>
       </c>
-      <c r="M18" s="12" t="s">
+      <c r="M18" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N18" s="2">
@@ -2198,45 +2213,45 @@
       <c r="U18" s="2">
         <v>0</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="V18" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="W18" s="13" t="s">
+      <c r="W18" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <v>24</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <v>3</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <v>76</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="9">
         <v>100</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="10">
         <v>7e+16</v>
       </c>
-      <c r="I19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="9">
+      <c r="I19" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="10">
         <v>3.5e+17</v>
       </c>
-      <c r="K19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="9">
+      <c r="K19" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10">
         <v>1.4e+22</v>
       </c>
-      <c r="M19" s="12" t="s">
+      <c r="M19" s="14" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2">
@@ -2263,58 +2278,58 @@
       <c r="U19" s="2">
         <v>0</v>
       </c>
-      <c r="V19" s="13" t="s">
+      <c r="V19" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="W19" s="13" t="s">
+      <c r="W19" s="15" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C21" s="8">
+      <c r="C21" s="9">
         <v>25</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="9">
         <v>4</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>1</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="9">
         <v>25</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="I21" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L21" s="12" t="s">
+      <c r="L21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="M21" s="12" t="s">
+      <c r="M21" s="14" t="s">
         <v>43</v>
       </c>
       <c r="N21" s="2">
@@ -2341,45 +2356,45 @@
       <c r="U21" s="2">
         <v>0</v>
       </c>
-      <c r="V21" s="13" t="s">
+      <c r="V21" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="W21" s="13" t="s">
+      <c r="W21" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C22" s="8">
-        <v>26</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="9">
+        <v>26</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="9">
         <v>4</v>
       </c>
-      <c r="F22" s="8">
-        <v>26</v>
-      </c>
-      <c r="G22" s="8">
+      <c r="F22" s="9">
+        <v>26</v>
+      </c>
+      <c r="G22" s="9">
         <v>50</v>
       </c>
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="I22" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="K22" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L22" s="12" t="s">
+      <c r="L22" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="14" t="s">
         <v>43</v>
       </c>
       <c r="N22" s="2">
@@ -2406,45 +2421,45 @@
       <c r="U22" s="2">
         <v>0</v>
       </c>
-      <c r="V22" s="13" t="s">
+      <c r="V22" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="W22" s="13" t="s">
+      <c r="W22" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C23" s="8">
+      <c r="C23" s="9">
         <v>27</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <v>4</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>51</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <v>75</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="K23" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L23" s="12" t="s">
+      <c r="L23" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="M23" s="14" t="s">
         <v>43</v>
       </c>
       <c r="N23" s="2">
@@ -2471,45 +2486,45 @@
       <c r="U23" s="2">
         <v>0</v>
       </c>
-      <c r="V23" s="13" t="s">
+      <c r="V23" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="W23" s="13" t="s">
+      <c r="W23" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C24" s="8">
+      <c r="C24" s="9">
         <v>28</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="9">
         <v>4</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>76</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="9">
         <v>100</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="I24" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K24" s="12" t="s">
+      <c r="K24" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="L24" s="12" t="s">
+      <c r="L24" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="M24" s="12" t="s">
+      <c r="M24" s="14" t="s">
         <v>43</v>
       </c>
       <c r="N24" s="2">
@@ -2536,58 +2551,58 @@
       <c r="U24" s="2">
         <v>0</v>
       </c>
-      <c r="V24" s="13" t="s">
+      <c r="V24" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="W24" s="13" t="s">
+      <c r="W24" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C26" s="8">
+      <c r="C26" s="9">
         <v>29</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="9">
         <v>5</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <v>1</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="9">
         <v>100</v>
       </c>
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="12">
         <v>2</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <v>2</v>
       </c>
-      <c r="L26" s="12" t="s">
+      <c r="L26" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="12" t="s">
+      <c r="M26" s="14" t="s">
         <v>61</v>
       </c>
       <c r="N26" s="2">
@@ -2614,64 +2629,116 @@
       <c r="U26" s="2">
         <v>99.9</v>
       </c>
-      <c r="V26" s="13" t="s">
+      <c r="V26" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="W26" s="13" t="s">
+      <c r="W26" s="15" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-    </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="C28" s="9">
+        <v>30</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="9">
+        <v>5</v>
+      </c>
+      <c r="F28" s="9">
+        <v>1</v>
+      </c>
+      <c r="G28" s="9">
+        <v>100</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K28" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N28" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O28" s="2">
+        <v>10000</v>
+      </c>
+      <c r="P28" s="2">
+        <v>10000</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>10000</v>
+      </c>
+      <c r="R28" s="2">
+        <v>200</v>
+      </c>
+      <c r="S28" s="2">
+        <v>180</v>
+      </c>
+      <c r="T28" s="2">
+        <v>99</v>
+      </c>
+      <c r="U28" s="2">
+        <v>99.999</v>
+      </c>
+      <c r="V28" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="W28" s="15" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="67">
   <si>
     <t>ID</t>
   </si>
@@ -221,7 +221,13 @@
     <t>永夜锤兵</t>
   </si>
   <si>
-    <t>9999那</t>
+    <t>9999沙</t>
+  </si>
+  <si>
+    <t>9999河</t>
+  </si>
+  <si>
+    <t>9999阿</t>
   </si>
   <si>
     <t>2</t>
@@ -2672,16 +2678,16 @@
         <v>1.5</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K28" s="12">
         <v>1.5</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N28" s="2">
         <v>10000</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="112">
   <si>
     <t>ID</t>
   </si>
@@ -360,6 +360,12 @@
   </si>
   <si>
     <t>1垓</t>
+  </si>
+  <si>
+    <t>虚无锤兵</t>
+  </si>
+  <si>
+    <t>600000000000000</t>
   </si>
 </sst>
 </file>
@@ -3243,17 +3249,91 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="8:17">
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:30">
+      <c r="C30" s="2">
+        <v>40</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E30" s="2">
+        <v>7</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>100</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" s="5">
+        <v>2</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="K30" s="5">
+        <v>1.2</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="N30" s="5">
+        <v>10</v>
+      </c>
+      <c r="O30" s="5">
+        <v>2.2</v>
+      </c>
+      <c r="P30" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>2</v>
+      </c>
+      <c r="R30" s="2">
+        <v>10000</v>
+      </c>
+      <c r="S30" s="2">
+        <v>10000</v>
+      </c>
+      <c r="T30" s="2">
+        <v>10000</v>
+      </c>
+      <c r="U30" s="2">
+        <v>10000</v>
+      </c>
+      <c r="V30" s="2">
+        <v>150</v>
+      </c>
+      <c r="W30" s="2">
+        <v>1</v>
+      </c>
+      <c r="X30" s="2">
+        <v>100</v>
+      </c>
+      <c r="Y30" s="2">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="2">
+        <v>99</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="AB30" s="2">
+        <v>250</v>
+      </c>
+      <c r="AC30" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD30" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="31" customHeight="1" spans="11:11">
       <c r="K31" s="6"/>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="120">
   <si>
     <t>ID</t>
   </si>
@@ -77,6 +77,12 @@
     <t>MulRise</t>
   </si>
   <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>ParryRise</t>
+  </si>
+  <si>
     <t>DamageIncrea</t>
   </si>
   <si>
@@ -363,6 +369,24 @@
   </si>
   <si>
     <t>虚无锤兵</t>
+  </si>
+  <si>
+    <t>1E+90</t>
+  </si>
+  <si>
+    <t>1E+110</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>1E+40</t>
+  </si>
+  <si>
+    <t>1E+50</t>
+  </si>
+  <si>
+    <t>1E+10</t>
   </si>
   <si>
     <t>600000000000000</t>
@@ -999,7 +1023,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1014,6 +1038,9 @@
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
@@ -1338,14 +1365,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AD31"/>
+  <dimension ref="C1:AF31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="3.125" style="1" customWidth="1"/>
     <col min="4" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="11.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1666666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.9166666666667" style="3" customWidth="1"/>
     <col min="9" max="9" width="9.375" style="3" customWidth="1"/>
     <col min="10" max="10" width="17.75" style="3" customWidth="1"/>
@@ -1356,21 +1384,23 @@
     <col min="15" max="15" width="9.41666666666667" style="3" customWidth="1"/>
     <col min="16" max="16" width="8" style="3" customWidth="1"/>
     <col min="17" max="17" width="8.33333333333333" style="3" customWidth="1"/>
-    <col min="18" max="18" width="7.25" style="1" customWidth="1"/>
-    <col min="19" max="19" width="8.875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="8" style="1" customWidth="1"/>
-    <col min="22" max="24" width="7.25" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.08333333333333" style="1" customWidth="1"/>
-    <col min="26" max="28" width="8.375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="15.5" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.375" style="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="1"/>
+    <col min="18" max="18" width="7.83333333333333" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.58333333333333" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7.25" style="1" customWidth="1"/>
+    <col min="21" max="21" width="8.875" style="1" customWidth="1"/>
+    <col min="22" max="22" width="6.375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="8" style="1" customWidth="1"/>
+    <col min="24" max="26" width="7.25" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.08333333333333" style="1" customWidth="1"/>
+    <col min="28" max="30" width="8.375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="15.5" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.375" style="1" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1"/>
     <row r="2" s="1" customFormat="1" customHeight="1"/>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1416,10 +1446,10 @@
       <c r="Q3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
       <c r="T3" s="4" t="s">
@@ -1455,10 +1485,16 @@
       <c r="AD3" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="AE3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C4" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
@@ -1502,10 +1538,10 @@
       <c r="Q4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="7" t="s">
         <v>16</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -1541,99 +1577,111 @@
       <c r="AD4" s="4" t="s">
         <v>27</v>
       </c>
+      <c r="AE4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:30">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="U5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="V5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O5" s="4" t="s">
+      <c r="W5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="4" t="s">
+      <c r="X5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="R5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="Y5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AA5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="AD5" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="AE5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
@@ -1644,23 +1692,23 @@
       <c r="G6" s="2">
         <v>25</v>
       </c>
-      <c r="H6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>34</v>
+      <c r="I6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N6" s="2">
         <v>0</v>
@@ -1674,12 +1722,6 @@
       <c r="Q6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="2">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
       <c r="T6" s="2">
         <v>0</v>
       </c>
@@ -1707,19 +1749,25 @@
       <c r="AB6" s="2">
         <v>0</v>
       </c>
-      <c r="AC6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD6" s="8" t="s">
-        <v>37</v>
+      <c r="AC6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF6" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
@@ -1730,23 +1778,23 @@
       <c r="G7" s="2">
         <v>50</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="7" t="s">
-        <v>34</v>
+      <c r="I7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N7" s="2">
         <v>0</v>
@@ -1760,15 +1808,9 @@
       <c r="Q7" s="2">
         <v>0</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>10</v>
       </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="2">
-        <v>0</v>
-      </c>
       <c r="U7" s="2">
         <v>0</v>
       </c>
@@ -1793,19 +1835,25 @@
       <c r="AB7" s="2">
         <v>0</v>
       </c>
-      <c r="AC7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="AD7" s="8" t="s">
-        <v>41</v>
+      <c r="AC7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF7" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
@@ -1816,23 +1864,23 @@
       <c r="G8" s="2">
         <v>75</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="7" t="s">
-        <v>34</v>
+      <c r="I8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N8" s="2">
         <v>0</v>
@@ -1846,15 +1894,9 @@
       <c r="Q8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="2">
+      <c r="T8" s="2">
         <v>20</v>
       </c>
-      <c r="S8" s="2">
-        <v>0</v>
-      </c>
-      <c r="T8" s="2">
-        <v>0</v>
-      </c>
       <c r="U8" s="2">
         <v>0</v>
       </c>
@@ -1879,19 +1921,25 @@
       <c r="AB8" s="2">
         <v>0</v>
       </c>
-      <c r="AC8" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>45</v>
+      <c r="AC8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF8" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
@@ -1902,23 +1950,23 @@
       <c r="G9" s="2">
         <v>100</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="7" t="s">
-        <v>34</v>
+      <c r="I9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N9" s="2">
         <v>0</v>
@@ -1932,24 +1980,18 @@
       <c r="Q9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="2">
+      <c r="T9" s="2">
         <v>75</v>
       </c>
-      <c r="S9" s="2">
+      <c r="U9" s="2">
         <v>10</v>
       </c>
-      <c r="T9" s="2">
+      <c r="V9" s="2">
         <v>15</v>
       </c>
-      <c r="U9" s="2">
+      <c r="W9" s="2">
         <v>15</v>
       </c>
-      <c r="V9" s="2">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2">
-        <v>0</v>
-      </c>
       <c r="X9" s="2">
         <v>0</v>
       </c>
@@ -1965,14 +2007,20 @@
       <c r="AB9" s="2">
         <v>0</v>
       </c>
-      <c r="AC9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD9" s="8" t="s">
-        <v>49</v>
+      <c r="AC9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF9" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="8:29">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="8:31">
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1983,14 +2031,14 @@
       <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
-      <c r="AC10" s="5"/>
+      <c r="AE10" s="5"/>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C11" s="2">
         <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="2">
         <v>2</v>
@@ -2001,23 +2049,23 @@
       <c r="G11" s="2">
         <v>25</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M11" s="7" t="s">
-        <v>34</v>
+      <c r="I11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N11" s="2">
         <v>0</v>
@@ -2031,24 +2079,18 @@
       <c r="Q11" s="2">
         <v>0</v>
       </c>
-      <c r="R11" s="2">
+      <c r="T11" s="2">
         <v>135</v>
       </c>
-      <c r="S11" s="2">
+      <c r="U11" s="2">
         <v>65</v>
       </c>
-      <c r="T11" s="2">
+      <c r="V11" s="2">
         <v>100</v>
       </c>
-      <c r="U11" s="2">
+      <c r="W11" s="2">
         <v>100</v>
       </c>
-      <c r="V11" s="2">
-        <v>0</v>
-      </c>
-      <c r="W11" s="2">
-        <v>0</v>
-      </c>
       <c r="X11" s="2">
         <v>0</v>
       </c>
@@ -2064,19 +2106,25 @@
       <c r="AB11" s="2">
         <v>0</v>
       </c>
-      <c r="AC11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="AD11" s="8" t="s">
-        <v>54</v>
+      <c r="AC11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="AF11" s="9" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C12" s="2">
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2">
         <v>2</v>
@@ -2087,23 +2135,23 @@
       <c r="G12" s="2">
         <v>50</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>34</v>
+      <c r="H12" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N12" s="2">
         <v>0</v>
@@ -2117,24 +2165,18 @@
       <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R12" s="2">
+      <c r="T12" s="2">
         <v>160</v>
       </c>
-      <c r="S12" s="2">
+      <c r="U12" s="2">
         <v>90</v>
       </c>
-      <c r="T12" s="2">
+      <c r="V12" s="2">
         <v>100</v>
       </c>
-      <c r="U12" s="2">
+      <c r="W12" s="2">
         <v>100</v>
       </c>
-      <c r="V12" s="2">
-        <v>0</v>
-      </c>
-      <c r="W12" s="2">
-        <v>0</v>
-      </c>
       <c r="X12" s="2">
         <v>0</v>
       </c>
@@ -2150,19 +2192,25 @@
       <c r="AB12" s="2">
         <v>0</v>
       </c>
-      <c r="AC12" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD12" s="8" t="s">
-        <v>57</v>
+      <c r="AC12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF12" s="9" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C13" s="2">
         <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" s="2">
         <v>2</v>
@@ -2173,23 +2221,23 @@
       <c r="G13" s="2">
         <v>75</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>34</v>
+      <c r="I13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N13" s="2">
         <v>0</v>
@@ -2203,24 +2251,18 @@
       <c r="Q13" s="2">
         <v>0</v>
       </c>
-      <c r="R13" s="2">
+      <c r="T13" s="2">
         <v>185</v>
       </c>
-      <c r="S13" s="2">
+      <c r="U13" s="2">
         <v>115</v>
       </c>
-      <c r="T13" s="2">
+      <c r="V13" s="2">
         <v>100</v>
       </c>
-      <c r="U13" s="2">
+      <c r="W13" s="2">
         <v>100</v>
       </c>
-      <c r="V13" s="2">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2">
-        <v>0</v>
-      </c>
       <c r="X13" s="2">
         <v>0</v>
       </c>
@@ -2236,19 +2278,25 @@
       <c r="AB13" s="2">
         <v>0</v>
       </c>
-      <c r="AC13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD13" s="8" t="s">
-        <v>61</v>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="AF13" s="9" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C14" s="2">
         <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -2259,23 +2307,23 @@
       <c r="G14" s="2">
         <v>100</v>
       </c>
-      <c r="H14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="M14" s="7" t="s">
-        <v>34</v>
+      <c r="I14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N14" s="2">
         <v>0</v>
@@ -2289,24 +2337,18 @@
       <c r="Q14" s="2">
         <v>0</v>
       </c>
-      <c r="R14" s="2">
+      <c r="T14" s="2">
         <v>209</v>
       </c>
-      <c r="S14" s="2">
+      <c r="U14" s="2">
         <v>139</v>
       </c>
-      <c r="T14" s="2">
+      <c r="V14" s="2">
         <v>100</v>
       </c>
-      <c r="U14" s="2">
+      <c r="W14" s="2">
         <v>100</v>
       </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
-        <v>0</v>
-      </c>
       <c r="X14" s="2">
         <v>0</v>
       </c>
@@ -2322,11 +2364,17 @@
       <c r="AB14" s="2">
         <v>0</v>
       </c>
-      <c r="AC14" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="AD14" s="8" t="s">
-        <v>65</v>
+      <c r="AC14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF14" s="9" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="8:17">
@@ -2341,12 +2389,12 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
     </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C16" s="2">
         <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2">
         <v>3</v>
@@ -2357,23 +2405,23 @@
       <c r="G16" s="2">
         <v>25</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="M16" s="7" t="s">
-        <v>34</v>
+      <c r="I16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N16" s="2">
         <v>0</v>
@@ -2387,24 +2435,18 @@
       <c r="Q16" s="2">
         <v>0</v>
       </c>
-      <c r="R16" s="2">
+      <c r="T16" s="2">
         <v>250</v>
       </c>
-      <c r="S16" s="2">
+      <c r="U16" s="2">
         <v>150</v>
       </c>
-      <c r="T16" s="2">
+      <c r="V16" s="2">
         <v>100</v>
       </c>
-      <c r="U16" s="2">
+      <c r="W16" s="2">
         <v>100</v>
       </c>
-      <c r="V16" s="2">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2">
-        <v>0</v>
-      </c>
       <c r="X16" s="2">
         <v>0</v>
       </c>
@@ -2412,27 +2454,33 @@
         <v>0</v>
       </c>
       <c r="Z16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="2">
         <v>80</v>
       </c>
-      <c r="AA16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD16" s="8" t="s">
-        <v>70</v>
+      <c r="AC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF16" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C17" s="2">
         <v>22</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2">
         <v>3</v>
@@ -2443,23 +2491,23 @@
       <c r="G17" s="2">
         <v>50</v>
       </c>
-      <c r="H17" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="M17" s="7" t="s">
-        <v>34</v>
+      <c r="I17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N17" s="2">
         <v>0</v>
@@ -2473,24 +2521,18 @@
       <c r="Q17" s="2">
         <v>0</v>
       </c>
-      <c r="R17" s="2">
+      <c r="T17" s="2">
         <v>300</v>
       </c>
-      <c r="S17" s="2">
+      <c r="U17" s="2">
         <v>200</v>
       </c>
-      <c r="T17" s="2">
+      <c r="V17" s="2">
         <v>125</v>
       </c>
-      <c r="U17" s="2">
+      <c r="W17" s="2">
         <v>125</v>
       </c>
-      <c r="V17" s="2">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2">
-        <v>0</v>
-      </c>
       <c r="X17" s="2">
         <v>0</v>
       </c>
@@ -2498,27 +2540,33 @@
         <v>0</v>
       </c>
       <c r="Z17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2">
         <v>80</v>
       </c>
-      <c r="AA17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AD17" s="8" t="s">
-        <v>74</v>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF17" s="9" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C18" s="2">
         <v>23</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2">
         <v>3</v>
@@ -2529,23 +2577,23 @@
       <c r="G18" s="2">
         <v>75</v>
       </c>
-      <c r="H18" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="M18" s="7" t="s">
-        <v>34</v>
+      <c r="I18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="N18" s="2">
         <v>0</v>
@@ -2559,24 +2607,18 @@
       <c r="Q18" s="2">
         <v>0</v>
       </c>
-      <c r="R18" s="2">
+      <c r="T18" s="2">
         <v>350</v>
       </c>
-      <c r="S18" s="2">
+      <c r="U18" s="2">
         <v>250</v>
       </c>
-      <c r="T18" s="2">
+      <c r="V18" s="2">
         <v>150</v>
       </c>
-      <c r="U18" s="2">
+      <c r="W18" s="2">
         <v>150</v>
       </c>
-      <c r="V18" s="2">
-        <v>0</v>
-      </c>
-      <c r="W18" s="2">
-        <v>0</v>
-      </c>
       <c r="X18" s="2">
         <v>0</v>
       </c>
@@ -2584,27 +2626,33 @@
         <v>0</v>
       </c>
       <c r="Z18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="2">
         <v>80</v>
       </c>
-      <c r="AA18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD18" s="8" t="s">
-        <v>78</v>
+      <c r="AC18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF18" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C19" s="2">
         <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2">
         <v>3</v>
@@ -2615,74 +2663,74 @@
       <c r="G19" s="2">
         <v>100</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="7" t="s">
+      <c r="H19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
+        <v>0</v>
+      </c>
+      <c r="P19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="T19" s="2">
+        <v>400</v>
+      </c>
+      <c r="U19" s="2">
+        <v>300</v>
+      </c>
+      <c r="V19" s="2">
+        <v>175</v>
+      </c>
+      <c r="W19" s="2">
+        <v>175</v>
+      </c>
+      <c r="X19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="2">
         <v>80</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N19" s="2">
-        <v>0</v>
-      </c>
-      <c r="O19" s="2">
-        <v>0</v>
-      </c>
-      <c r="P19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>0</v>
-      </c>
-      <c r="R19" s="2">
-        <v>400</v>
-      </c>
-      <c r="S19" s="2">
-        <v>300</v>
-      </c>
-      <c r="T19" s="2">
-        <v>175</v>
-      </c>
-      <c r="U19" s="2">
-        <v>175</v>
-      </c>
-      <c r="V19" s="2">
-        <v>0</v>
-      </c>
-      <c r="W19" s="2">
-        <v>0</v>
-      </c>
-      <c r="X19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD19" s="8" t="s">
-        <v>82</v>
+      <c r="AC19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF19" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="8:17">
@@ -2697,12 +2745,12 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C21" s="2">
         <v>25</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2">
         <v>4</v>
@@ -2713,23 +2761,23 @@
       <c r="G21" s="2">
         <v>25</v>
       </c>
-      <c r="H21" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J21" s="7" t="s">
+      <c r="H21" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L21" s="7" t="s">
+      <c r="I21" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="M21" s="7" t="s">
-        <v>85</v>
+      <c r="J21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="N21" s="2">
         <v>0</v>
@@ -2743,23 +2791,17 @@
       <c r="Q21" s="2">
         <v>0</v>
       </c>
-      <c r="R21" s="2">
+      <c r="T21" s="2">
         <v>600</v>
       </c>
-      <c r="S21" s="2">
+      <c r="U21" s="2">
         <v>600</v>
       </c>
-      <c r="T21" s="2">
+      <c r="V21" s="2">
         <v>100</v>
       </c>
-      <c r="U21" s="2">
+      <c r="W21" s="2">
         <v>100</v>
-      </c>
-      <c r="V21" s="2">
-        <v>40</v>
-      </c>
-      <c r="W21" s="2">
-        <v>0</v>
       </c>
       <c r="X21" s="2">
         <v>40</v>
@@ -2768,27 +2810,33 @@
         <v>0</v>
       </c>
       <c r="Z21" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2">
         <v>80</v>
       </c>
-      <c r="AA21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD21" s="8" t="s">
-        <v>88</v>
+      <c r="AC21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF21" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C22" s="2">
         <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2">
         <v>4</v>
@@ -2799,23 +2847,23 @@
       <c r="G22" s="2">
         <v>50</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="M22" s="7" t="s">
-        <v>85</v>
+      <c r="I22" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="N22" s="2">
         <v>0</v>
@@ -2829,23 +2877,17 @@
       <c r="Q22" s="2">
         <v>0</v>
       </c>
-      <c r="R22" s="2">
+      <c r="T22" s="2">
         <v>700</v>
       </c>
-      <c r="S22" s="2">
+      <c r="U22" s="2">
         <v>700</v>
       </c>
-      <c r="T22" s="2">
+      <c r="V22" s="2">
         <v>125</v>
       </c>
-      <c r="U22" s="2">
+      <c r="W22" s="2">
         <v>125</v>
-      </c>
-      <c r="V22" s="2">
-        <v>40</v>
-      </c>
-      <c r="W22" s="2">
-        <v>0</v>
       </c>
       <c r="X22" s="2">
         <v>40</v>
@@ -2854,27 +2896,33 @@
         <v>0</v>
       </c>
       <c r="Z22" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="2">
         <v>80</v>
       </c>
-      <c r="AA22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD22" s="8" t="s">
-        <v>92</v>
+      <c r="AC22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF22" s="9" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C23" s="2">
         <v>27</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2">
         <v>4</v>
@@ -2885,23 +2933,23 @@
       <c r="G23" s="2">
         <v>75</v>
       </c>
-      <c r="H23" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="7" t="s">
+      <c r="H23" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="M23" s="7" t="s">
-        <v>85</v>
+      <c r="I23" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="N23" s="2">
         <v>0</v>
@@ -2915,23 +2963,17 @@
       <c r="Q23" s="2">
         <v>0</v>
       </c>
-      <c r="R23" s="2">
+      <c r="T23" s="2">
         <v>800</v>
       </c>
-      <c r="S23" s="2">
+      <c r="U23" s="2">
         <v>800</v>
       </c>
-      <c r="T23" s="2">
+      <c r="V23" s="2">
         <v>150</v>
       </c>
-      <c r="U23" s="2">
+      <c r="W23" s="2">
         <v>150</v>
-      </c>
-      <c r="V23" s="2">
-        <v>40</v>
-      </c>
-      <c r="W23" s="2">
-        <v>0</v>
       </c>
       <c r="X23" s="2">
         <v>40</v>
@@ -2940,27 +2982,33 @@
         <v>0</v>
       </c>
       <c r="Z23" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2">
         <v>80</v>
       </c>
-      <c r="AA23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD23" s="8" t="s">
-        <v>96</v>
+      <c r="AC23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF23" s="9" t="s">
+        <v>98</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C24" s="2">
         <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2">
         <v>4</v>
@@ -2971,23 +3019,23 @@
       <c r="G24" s="2">
         <v>100</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I24" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>85</v>
+      <c r="J24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="N24" s="2">
         <v>0</v>
@@ -3001,23 +3049,17 @@
       <c r="Q24" s="2">
         <v>0</v>
       </c>
-      <c r="R24" s="2">
+      <c r="T24" s="2">
         <v>900</v>
       </c>
-      <c r="S24" s="2">
+      <c r="U24" s="2">
         <v>900</v>
       </c>
-      <c r="T24" s="2">
+      <c r="V24" s="2">
         <v>175</v>
       </c>
-      <c r="U24" s="2">
+      <c r="W24" s="2">
         <v>175</v>
-      </c>
-      <c r="V24" s="2">
-        <v>40</v>
-      </c>
-      <c r="W24" s="2">
-        <v>0</v>
       </c>
       <c r="X24" s="2">
         <v>40</v>
@@ -3026,19 +3068,25 @@
         <v>0</v>
       </c>
       <c r="Z24" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="2">
         <v>80</v>
       </c>
-      <c r="AA24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD24" s="8" t="s">
-        <v>99</v>
+      <c r="AC24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF24" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="8:17">
@@ -3053,12 +3101,12 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C26" s="2">
         <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E26" s="2">
         <v>5</v>
@@ -3069,23 +3117,23 @@
       <c r="G26" s="2">
         <v>100</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>95</v>
+      <c r="H26" s="8" t="s">
+        <v>97</v>
       </c>
       <c r="I26" s="5">
         <v>2</v>
       </c>
-      <c r="J26" s="7" t="s">
-        <v>101</v>
+      <c r="J26" s="8" t="s">
+        <v>103</v>
       </c>
       <c r="K26" s="5">
         <v>2</v>
       </c>
-      <c r="L26" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>103</v>
+      <c r="L26" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>105</v>
       </c>
       <c r="N26" s="2">
         <v>0</v>
@@ -3098,12 +3146,6 @@
       </c>
       <c r="Q26" s="2">
         <v>0</v>
-      </c>
-      <c r="R26" s="2">
-        <v>5000</v>
-      </c>
-      <c r="S26" s="2">
-        <v>5000</v>
       </c>
       <c r="T26" s="2">
         <v>5000</v>
@@ -3112,31 +3154,37 @@
         <v>5000</v>
       </c>
       <c r="V26" s="2">
+        <v>5000</v>
+      </c>
+      <c r="W26" s="2">
+        <v>5000</v>
+      </c>
+      <c r="X26" s="2">
         <v>100</v>
       </c>
-      <c r="W26" s="2">
-        <v>0</v>
-      </c>
-      <c r="X26" s="2">
+      <c r="Y26" s="2">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2">
         <v>80</v>
       </c>
-      <c r="Y26" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="2">
+      <c r="AA26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="2">
         <v>99</v>
       </c>
-      <c r="AA26" s="2">
+      <c r="AC26" s="2">
         <v>99.9</v>
       </c>
-      <c r="AB26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="AD26" s="8" t="s">
-        <v>92</v>
+      <c r="AD26" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF26" s="9" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" customHeight="1" spans="8:17">
@@ -3151,12 +3199,12 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
     </row>
-    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C28" s="2">
         <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2">
         <v>6</v>
@@ -3168,22 +3216,22 @@
         <v>100</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I28" s="5">
         <v>1.2</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K28" s="5">
         <v>1.2</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="N28" s="5">
         <v>10</v>
@@ -3192,17 +3240,11 @@
         <v>2.2</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="5">
         <v>2</v>
       </c>
-      <c r="R28" s="2">
-        <v>10000</v>
-      </c>
-      <c r="S28" s="2">
-        <v>10000</v>
-      </c>
       <c r="T28" s="2">
         <v>10000</v>
       </c>
@@ -3210,31 +3252,37 @@
         <v>10000</v>
       </c>
       <c r="V28" s="2">
+        <v>10000</v>
+      </c>
+      <c r="W28" s="2">
+        <v>10000</v>
+      </c>
+      <c r="X28" s="2">
         <v>150</v>
-      </c>
-      <c r="W28" s="2">
-        <v>1</v>
-      </c>
-      <c r="X28" s="2">
-        <v>100</v>
       </c>
       <c r="Y28" s="2">
         <v>1</v>
       </c>
       <c r="Z28" s="2">
+        <v>100</v>
+      </c>
+      <c r="AA28" s="2">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="2">
         <v>99</v>
       </c>
-      <c r="AA28" s="2">
+      <c r="AC28" s="2">
         <v>99.9</v>
       </c>
-      <c r="AB28" s="2">
+      <c r="AD28" s="2">
         <v>100</v>
       </c>
-      <c r="AC28" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD28" s="8" t="s">
-        <v>99</v>
+      <c r="AE28" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF28" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="8:17">
@@ -3249,12 +3297,12 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:30">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C30" s="2">
         <v>40</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E30" s="2">
         <v>7</v>
@@ -3265,74 +3313,80 @@
       <c r="G30" s="2">
         <v>100</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>105</v>
+      <c r="H30" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="I30" s="5">
+        <v>4</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="K30" s="5">
+        <v>4</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="O30" s="5">
+        <v>3</v>
+      </c>
+      <c r="P30" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>3</v>
+      </c>
+      <c r="R30" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S30" s="2">
         <v>2</v>
       </c>
-      <c r="J30" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="K30" s="5">
-        <v>1.2</v>
-      </c>
-      <c r="L30" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="N30" s="5">
-        <v>10</v>
-      </c>
-      <c r="O30" s="5">
-        <v>2.2</v>
-      </c>
-      <c r="P30" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q30" s="5">
+      <c r="T30" s="2">
+        <v>30000</v>
+      </c>
+      <c r="U30" s="2">
+        <v>30000</v>
+      </c>
+      <c r="V30" s="2">
+        <v>30000</v>
+      </c>
+      <c r="W30" s="2">
+        <v>30000</v>
+      </c>
+      <c r="X30" s="2">
+        <v>350</v>
+      </c>
+      <c r="Y30" s="2">
         <v>2</v>
       </c>
-      <c r="R30" s="2">
-        <v>10000</v>
-      </c>
-      <c r="S30" s="2">
-        <v>10000</v>
-      </c>
-      <c r="T30" s="2">
-        <v>10000</v>
-      </c>
-      <c r="U30" s="2">
-        <v>10000</v>
-      </c>
-      <c r="V30" s="2">
-        <v>150</v>
-      </c>
-      <c r="W30" s="2">
-        <v>1</v>
-      </c>
-      <c r="X30" s="2">
-        <v>100</v>
-      </c>
-      <c r="Y30" s="2">
-        <v>1</v>
-      </c>
       <c r="Z30" s="2">
+        <v>300</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>2</v>
+      </c>
+      <c r="AB30" s="2">
         <v>99</v>
       </c>
-      <c r="AA30" s="2">
+      <c r="AC30" s="2">
         <v>99.9</v>
       </c>
-      <c r="AB30" s="2">
+      <c r="AD30" s="2">
         <v>250</v>
       </c>
-      <c r="AC30" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AD30" s="8" t="s">
-        <v>111</v>
+      <c r="AE30" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF30" s="9" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="11:11">
@@ -3340,7 +3394,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AB5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3 S3 R4 S4 R5 S5 C3:Q5 T3:AD5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="121">
   <si>
     <t>ID</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>虚无锤兵</t>
+  </si>
+  <si>
+    <t>1E+80</t>
   </si>
   <si>
     <t>1E+90</t>
@@ -3317,34 +3320,34 @@
         <v>113</v>
       </c>
       <c r="I30" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K30" s="5">
         <v>4</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O30" s="5">
         <v>3</v>
       </c>
       <c r="P30" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="5">
         <v>3</v>
       </c>
       <c r="R30" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="S30" s="2">
         <v>2</v>
@@ -3383,10 +3386,10 @@
         <v>250</v>
       </c>
       <c r="AE30" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AF30" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="11:11">
@@ -3394,7 +3397,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3 S3 R4 S4 R5 S5 C3:Q5 T3:AD5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3:S3 C3:Q5 R4:S5 T3:AD5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -3320,7 +3320,7 @@
         <v>113</v>
       </c>
       <c r="I30" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>114</v>
@@ -3338,7 +3338,7 @@
         <v>117</v>
       </c>
       <c r="O30" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" s="8" t="s">
         <v>118</v>
@@ -3350,7 +3350,7 @@
         <v>119</v>
       </c>
       <c r="S30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" s="2">
         <v>30000</v>
@@ -3397,7 +3397,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="R3:S3 C3:Q5 R4:S5 T3:AD5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:AD5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -377,19 +377,19 @@
     <t>1E+90</t>
   </si>
   <si>
-    <t>1E+110</t>
+    <t>1E+105</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>1E+40</t>
-  </si>
-  <si>
-    <t>1E+50</t>
-  </si>
-  <si>
-    <t>1E+10</t>
+    <t>1E+27</t>
+  </si>
+  <si>
+    <t>1E+57</t>
+  </si>
+  <si>
+    <t>1E+13</t>
   </si>
   <si>
     <t>600000000000000</t>
@@ -3320,7 +3320,7 @@
         <v>113</v>
       </c>
       <c r="I30" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>114</v>
@@ -3350,28 +3350,28 @@
         <v>119</v>
       </c>
       <c r="S30" s="2">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T30" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="U30" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="V30" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="W30" s="2">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="X30" s="2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="Y30" s="2">
         <v>2</v>
       </c>
       <c r="Z30" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AA30" s="2">
         <v>2</v>
@@ -3383,7 +3383,7 @@
         <v>99.9</v>
       </c>
       <c r="AD30" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="AE30" s="9" t="s">
         <v>120</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -371,7 +371,7 @@
     <t>虚无锤兵</t>
   </si>
   <si>
-    <t>1E+80</t>
+    <t>1E+78</t>
   </si>
   <si>
     <t>1E+90</t>
@@ -383,10 +383,10 @@
     <t>4</t>
   </si>
   <si>
-    <t>1E+27</t>
-  </si>
-  <si>
-    <t>1E+57</t>
+    <t>1E+23</t>
+  </si>
+  <si>
+    <t>1E+55</t>
   </si>
   <si>
     <t>1E+13</t>
@@ -3344,7 +3344,7 @@
         <v>118</v>
       </c>
       <c r="Q30" s="5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R30" s="9" t="s">
         <v>119</v>
@@ -3368,7 +3368,7 @@
         <v>300</v>
       </c>
       <c r="Y30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z30" s="2">
         <v>250</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -3344,7 +3344,7 @@
         <v>118</v>
       </c>
       <c r="Q30" s="5">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R30" s="9" t="s">
         <v>119</v>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="128">
   <si>
     <t>ID</t>
   </si>
@@ -393,6 +393,27 @@
   </si>
   <si>
     <t>600000000000000</t>
+  </si>
+  <si>
+    <t>寂灭锤兵</t>
+  </si>
+  <si>
+    <t>1E+126</t>
+  </si>
+  <si>
+    <t>1E+150</t>
+  </si>
+  <si>
+    <t>1E+165</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1E+107</t>
+  </si>
+  <si>
+    <t>800000000000000</t>
   </si>
 </sst>
 </file>
@@ -1036,14 +1057,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
@@ -1368,7 +1389,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AF31"/>
+  <dimension ref="C1:AF32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.875" style="1" customWidth="1"/>
@@ -1449,10 +1470,10 @@
       <c r="Q3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="R3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="S3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="T3" s="4" t="s">
@@ -1541,10 +1562,10 @@
       <c r="Q4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="T4" s="4" t="s">
@@ -2023,18 +2044,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="8:31">
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="AE10" s="5"/>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="AE10" s="6"/>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C11" s="2">
@@ -2380,17 +2401,17 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="8:17">
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C16" s="2">
@@ -2736,17 +2757,17 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="8:17">
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C21" s="2">
@@ -3092,17 +3113,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="8:17">
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C26" s="2">
@@ -3123,13 +3144,13 @@
       <c r="H26" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="6">
         <v>2</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="6">
         <v>2</v>
       </c>
       <c r="L26" s="8" t="s">
@@ -3190,17 +3211,17 @@
         <v>94</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" customHeight="1" spans="8:17">
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-      <c r="L27" s="5"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
     </row>
     <row r="28" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C28" s="2">
@@ -3218,34 +3239,34 @@
       <c r="G28" s="2">
         <v>100</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="6">
         <v>1.2</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="6">
         <v>1.2</v>
       </c>
-      <c r="L28" s="5" t="s">
+      <c r="L28" s="6" t="s">
         <v>109</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="6">
         <v>10</v>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="6">
         <v>2.2</v>
       </c>
-      <c r="P28" s="5" t="s">
+      <c r="P28" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="Q28" s="5">
+      <c r="Q28" s="6">
         <v>2</v>
       </c>
       <c r="T28" s="2">
@@ -3288,17 +3309,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="8:17">
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="5"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
     </row>
     <row r="30" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="C30" s="2">
@@ -3319,13 +3340,13 @@
       <c r="H30" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="6">
         <v>3</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="6">
         <v>4</v>
       </c>
       <c r="L30" s="8" t="s">
@@ -3337,13 +3358,13 @@
       <c r="N30" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="O30" s="5">
+      <c r="O30" s="6">
         <v>2</v>
       </c>
       <c r="P30" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="Q30" s="5">
+      <c r="Q30" s="6">
         <v>3.3</v>
       </c>
       <c r="R30" s="9" t="s">
@@ -3392,8 +3413,100 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="11:11">
-      <c r="K31" s="6"/>
+    <row r="31" customHeight="1" spans="3:32">
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="C32" s="2">
+        <v>50</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="2">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>100</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="I32" s="6">
+        <v>3</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K32" s="6">
+        <v>1</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="O32" s="6">
+        <v>2</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>3</v>
+      </c>
+      <c r="R32" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="S32" s="2">
+        <v>3</v>
+      </c>
+      <c r="T32" s="2">
+        <v>200000</v>
+      </c>
+      <c r="U32" s="2">
+        <v>200000</v>
+      </c>
+      <c r="V32" s="2">
+        <v>200000</v>
+      </c>
+      <c r="W32" s="2">
+        <v>200000</v>
+      </c>
+      <c r="X32" s="2">
+        <v>600</v>
+      </c>
+      <c r="Y32" s="2">
+        <v>4</v>
+      </c>
+      <c r="Z32" s="2">
+        <v>450</v>
+      </c>
+      <c r="AA32" s="2">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="2">
+        <v>99</v>
+      </c>
+      <c r="AC32" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="AD32" s="2">
+        <v>300</v>
+      </c>
+      <c r="AE32" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF32" s="9" t="s">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="134">
   <si>
     <t>ID</t>
   </si>
@@ -414,6 +414,50 @@
   </si>
   <si>
     <t>800000000000000</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>造化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>锤兵</t>
+    </r>
+  </si>
+  <si>
+    <t>1E+180</t>
+  </si>
+  <si>
+    <t>1E+220</t>
+  </si>
+  <si>
+    <t>1E+100</t>
+  </si>
+  <si>
+    <t>1E+160</t>
+  </si>
+  <si>
+    <t>1000000000000000</t>
   </si>
 </sst>
 </file>
@@ -427,7 +471,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,6 +490,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -591,6 +641,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -917,137 +973,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1066,6 +1122,7 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1389,7 +1446,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:AF32"/>
+  <dimension ref="C1:AF34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.875" style="1" customWidth="1"/>
@@ -1716,22 +1773,22 @@
       <c r="G6" s="2">
         <v>25</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N6" s="2">
@@ -1779,10 +1836,10 @@
       <c r="AD6" s="2">
         <v>0</v>
       </c>
-      <c r="AE6" s="9" t="s">
+      <c r="AE6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="AF6" s="9" t="s">
+      <c r="AF6" s="10" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1802,22 +1859,22 @@
       <c r="G7" s="2">
         <v>50</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="L7" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N7" s="2">
@@ -1865,10 +1922,10 @@
       <c r="AD7" s="2">
         <v>0</v>
       </c>
-      <c r="AE7" s="9" t="s">
+      <c r="AE7" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="AF7" s="9" t="s">
+      <c r="AF7" s="10" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1888,22 +1945,22 @@
       <c r="G8" s="2">
         <v>75</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="8" t="s">
+      <c r="L8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="8" t="s">
+      <c r="M8" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N8" s="2">
@@ -1951,10 +2008,10 @@
       <c r="AD8" s="2">
         <v>0</v>
       </c>
-      <c r="AE8" s="9" t="s">
+      <c r="AE8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AF8" s="9" t="s">
+      <c r="AF8" s="10" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1974,22 +2031,22 @@
       <c r="G9" s="2">
         <v>100</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="L9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N9" s="2">
@@ -2037,10 +2094,10 @@
       <c r="AD9" s="2">
         <v>0</v>
       </c>
-      <c r="AE9" s="9" t="s">
+      <c r="AE9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="AF9" s="9" t="s">
+      <c r="AF9" s="10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2073,22 +2130,22 @@
       <c r="G11" s="2">
         <v>25</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N11" s="2">
@@ -2136,10 +2193,10 @@
       <c r="AD11" s="2">
         <v>0</v>
       </c>
-      <c r="AE11" s="9" t="s">
+      <c r="AE11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="AF11" s="9" t="s">
+      <c r="AF11" s="10" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2159,22 +2216,22 @@
       <c r="G12" s="2">
         <v>50</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L12" s="8" t="s">
+      <c r="L12" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="M12" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N12" s="2">
@@ -2222,10 +2279,10 @@
       <c r="AD12" s="2">
         <v>0</v>
       </c>
-      <c r="AE12" s="9" t="s">
+      <c r="AE12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="AF12" s="9" t="s">
+      <c r="AF12" s="10" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2245,22 +2302,22 @@
       <c r="G13" s="2">
         <v>75</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="M13" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N13" s="2">
@@ -2308,10 +2365,10 @@
       <c r="AD13" s="2">
         <v>0</v>
       </c>
-      <c r="AE13" s="9" t="s">
+      <c r="AE13" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AF13" s="9" t="s">
+      <c r="AF13" s="10" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2331,22 +2388,22 @@
       <c r="G14" s="2">
         <v>100</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="K14" s="8" t="s">
+      <c r="K14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="8" t="s">
+      <c r="L14" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="M14" s="8" t="s">
+      <c r="M14" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N14" s="2">
@@ -2394,10 +2451,10 @@
       <c r="AD14" s="2">
         <v>0</v>
       </c>
-      <c r="AE14" s="9" t="s">
+      <c r="AE14" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="AF14" s="9" t="s">
+      <c r="AF14" s="10" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2429,22 +2486,22 @@
       <c r="G16" s="2">
         <v>25</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="8" t="s">
+      <c r="M16" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N16" s="2">
@@ -2492,10 +2549,10 @@
       <c r="AD16" s="2">
         <v>0</v>
       </c>
-      <c r="AE16" s="9" t="s">
+      <c r="AE16" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="AF16" s="9" t="s">
+      <c r="AF16" s="10" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2515,22 +2572,22 @@
       <c r="G17" s="2">
         <v>50</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L17" s="8" t="s">
+      <c r="L17" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="M17" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N17" s="2">
@@ -2578,10 +2635,10 @@
       <c r="AD17" s="2">
         <v>0</v>
       </c>
-      <c r="AE17" s="9" t="s">
+      <c r="AE17" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AF17" s="9" t="s">
+      <c r="AF17" s="10" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2601,22 +2658,22 @@
       <c r="G18" s="2">
         <v>75</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="L18" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="M18" s="8" t="s">
+      <c r="M18" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N18" s="2">
@@ -2664,10 +2721,10 @@
       <c r="AD18" s="2">
         <v>0</v>
       </c>
-      <c r="AE18" s="9" t="s">
+      <c r="AE18" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="AF18" s="9" t="s">
+      <c r="AF18" s="10" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2687,22 +2744,22 @@
       <c r="G19" s="2">
         <v>100</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L19" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="M19" s="8" t="s">
+      <c r="M19" s="9" t="s">
         <v>36</v>
       </c>
       <c r="N19" s="2">
@@ -2750,10 +2807,10 @@
       <c r="AD19" s="2">
         <v>0</v>
       </c>
-      <c r="AE19" s="9" t="s">
+      <c r="AE19" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="AF19" s="9" t="s">
+      <c r="AF19" s="10" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2785,22 +2842,22 @@
       <c r="G21" s="2">
         <v>25</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L21" s="8" t="s">
+      <c r="L21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="M21" s="8" t="s">
+      <c r="M21" s="9" t="s">
         <v>87</v>
       </c>
       <c r="N21" s="2">
@@ -2848,10 +2905,10 @@
       <c r="AD21" s="2">
         <v>0</v>
       </c>
-      <c r="AE21" s="9" t="s">
+      <c r="AE21" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="AF21" s="9" t="s">
+      <c r="AF21" s="10" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2871,22 +2928,22 @@
       <c r="G22" s="2">
         <v>50</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L22" s="8" t="s">
+      <c r="L22" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="M22" s="9" t="s">
         <v>87</v>
       </c>
       <c r="N22" s="2">
@@ -2934,10 +2991,10 @@
       <c r="AD22" s="2">
         <v>0</v>
       </c>
-      <c r="AE22" s="9" t="s">
+      <c r="AE22" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="AF22" s="9" t="s">
+      <c r="AF22" s="10" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2957,22 +3014,22 @@
       <c r="G23" s="2">
         <v>75</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="I23" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="L23" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="M23" s="9" t="s">
         <v>87</v>
       </c>
       <c r="N23" s="2">
@@ -3020,10 +3077,10 @@
       <c r="AD23" s="2">
         <v>0</v>
       </c>
-      <c r="AE23" s="9" t="s">
+      <c r="AE23" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="AF23" s="9" t="s">
+      <c r="AF23" s="10" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3043,22 +3100,22 @@
       <c r="G24" s="2">
         <v>100</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="I24" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="L24" s="8" t="s">
+      <c r="L24" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="M24" s="8" t="s">
+      <c r="M24" s="9" t="s">
         <v>87</v>
       </c>
       <c r="N24" s="2">
@@ -3106,10 +3163,10 @@
       <c r="AD24" s="2">
         <v>0</v>
       </c>
-      <c r="AE24" s="9" t="s">
+      <c r="AE24" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="AF24" s="9" t="s">
+      <c r="AF24" s="10" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3141,22 +3198,22 @@
       <c r="G26" s="2">
         <v>100</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>97</v>
       </c>
       <c r="I26" s="6">
         <v>2</v>
       </c>
-      <c r="J26" s="8" t="s">
+      <c r="J26" s="9" t="s">
         <v>103</v>
       </c>
       <c r="K26" s="6">
         <v>2</v>
       </c>
-      <c r="L26" s="8" t="s">
+      <c r="L26" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="M26" s="9" t="s">
         <v>105</v>
       </c>
       <c r="N26" s="2">
@@ -3204,10 +3261,10 @@
       <c r="AD26" s="2">
         <v>0</v>
       </c>
-      <c r="AE26" s="9" t="s">
+      <c r="AE26" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="AF26" s="9" t="s">
+      <c r="AF26" s="10" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3254,7 +3311,7 @@
       <c r="L28" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="M28" s="8" t="s">
+      <c r="M28" s="9" t="s">
         <v>110</v>
       </c>
       <c r="N28" s="6">
@@ -3302,10 +3359,10 @@
       <c r="AD28" s="2">
         <v>100</v>
       </c>
-      <c r="AE28" s="9" t="s">
+      <c r="AE28" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="AF28" s="9" t="s">
+      <c r="AF28" s="10" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3337,37 +3394,37 @@
       <c r="G30" s="2">
         <v>100</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="9" t="s">
         <v>113</v>
       </c>
       <c r="I30" s="6">
         <v>3</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="J30" s="9" t="s">
         <v>114</v>
       </c>
       <c r="K30" s="6">
         <v>4</v>
       </c>
-      <c r="L30" s="8" t="s">
+      <c r="L30" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="M30" s="8" t="s">
+      <c r="M30" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="N30" s="9" t="s">
         <v>117</v>
       </c>
       <c r="O30" s="6">
         <v>2</v>
       </c>
-      <c r="P30" s="8" t="s">
+      <c r="P30" s="9" t="s">
         <v>118</v>
       </c>
       <c r="Q30" s="6">
         <v>3.3</v>
       </c>
-      <c r="R30" s="9" t="s">
+      <c r="R30" s="10" t="s">
         <v>119</v>
       </c>
       <c r="S30" s="2">
@@ -3406,10 +3463,10 @@
       <c r="AD30" s="2">
         <v>200</v>
       </c>
-      <c r="AE30" s="9" t="s">
+      <c r="AE30" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="AF30" s="9" t="s">
+      <c r="AF30" s="10" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3432,37 +3489,37 @@
       <c r="G32" s="2">
         <v>100</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="9" t="s">
         <v>122</v>
       </c>
       <c r="I32" s="6">
         <v>3</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="J32" s="9" t="s">
         <v>123</v>
       </c>
       <c r="K32" s="6">
         <v>1</v>
       </c>
-      <c r="L32" s="8" t="s">
+      <c r="L32" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="M32" s="8" t="s">
+      <c r="M32" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="N32" s="9" t="s">
         <v>118</v>
       </c>
       <c r="O32" s="6">
         <v>2</v>
       </c>
-      <c r="P32" s="8" t="s">
+      <c r="P32" s="9" t="s">
         <v>126</v>
       </c>
       <c r="Q32" s="6">
         <v>3</v>
       </c>
-      <c r="R32" s="9" t="s">
+      <c r="R32" s="10" t="s">
         <v>118</v>
       </c>
       <c r="S32" s="2">
@@ -3501,11 +3558,103 @@
       <c r="AD32" s="2">
         <v>300</v>
       </c>
-      <c r="AE32" s="9" t="s">
+      <c r="AE32" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="AF32" s="9" t="s">
+      <c r="AF32" s="10" t="s">
         <v>127</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:32">
+      <c r="C34" s="2">
+        <v>60</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E34" s="2">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>100</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="I34" s="6">
+        <v>3</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="K34" s="6">
+        <v>1</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="O34" s="2">
+        <v>3</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>3</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="S34" s="2">
+        <v>3</v>
+      </c>
+      <c r="T34" s="2">
+        <v>400000</v>
+      </c>
+      <c r="U34" s="2">
+        <v>400000</v>
+      </c>
+      <c r="V34" s="2">
+        <v>400000</v>
+      </c>
+      <c r="W34" s="2">
+        <v>400000</v>
+      </c>
+      <c r="X34" s="2">
+        <v>900</v>
+      </c>
+      <c r="Y34" s="2">
+        <v>5</v>
+      </c>
+      <c r="Z34" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA34" s="2">
+        <v>4</v>
+      </c>
+      <c r="AB34" s="2">
+        <v>99</v>
+      </c>
+      <c r="AC34" s="2">
+        <v>99.9</v>
+      </c>
+      <c r="AD34" s="2">
+        <v>300</v>
+      </c>
+      <c r="AE34" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF34" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DefendConfig.xlsx
+++ b/Excel/DefendConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="134">
   <si>
     <t>ID</t>
   </si>
@@ -3596,14 +3596,14 @@
       <c r="L34" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="M34" s="9" t="s">
-        <v>125</v>
+      <c r="M34" s="6">
+        <v>4</v>
       </c>
       <c r="N34" s="9" t="s">
         <v>131</v>
       </c>
       <c r="O34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34" s="9" t="s">
         <v>132</v>
@@ -3615,7 +3615,7 @@
         <v>131</v>
       </c>
       <c r="S34" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T34" s="2">
         <v>400000</v>
